--- a/rostender_results.xlsx
+++ b/rostender_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,7926 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому и программно-методическому обеспечению проведения стратегической проектировочной сессии с управленческими командами педагогических вузов (в рамках федерального проекта "педагоги и наставники" национального проекта "молодежь и дети") в Москве</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94531639-tender-okazanie-uslug-po-organizacionno-tehnicheskomu-i-programmno-metodicheskomu-obespecheniyu-provedeniya-strategicheskoj-proektirovochnoj-sessii</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>19 820 962 ₽</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъёмке концертов и торжественных мероприятий в рамках музыкального фестиваля, посвящённого 100?летию санкт?петербургского музыкального училища имени м.п.мусоргского и созданию итогового видеоролика и фильма в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94531888-tender-okazanie-uslug-po-videosemke-koncertov-i-torjestvennyh-meropriyatij-v-ramkah-muzykalnogo-festivalya-posvyashchennogo-100letiyu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>198 000 ₽</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и изготовлению видеороликов в рамках проведения ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов в Уфе</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94505766-tender-okazanie-uslug-po-videosemke-i-izgotovleniyu-videorolikov-v-ramkah-provedeniya-ii-vserossijskoj-spartakiady-mejdu-subektami</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>360 000 ₽</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению церемонии награждения премии общественной палаты новосибирской области за вклад в развитие благотворительности и добровольчества новосибирской области "во благо" в Новосибирске</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>/region/novosibirskaya-oblast/novosibirsk/94501659-tender-okazanie-uslug-po-organizacii-i-provedeniyu-ceremonii-nagrajdeniya-premii-obshchestvennoj-palaty-novosibirskoj-oblasti</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>240 720 ₽</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации фотосъемки и видеосъемки всероссийского профессионального конкурса лучший учитель родного языка и родной литературы в 2026 году в Липецке</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>/region/lipeckaya-oblast/lipeck/94502505-tender-okazanie-uslug-po-organizacii-fotosemki-i-videosemki-vserossijskogo-professionalnogo-konkursa-luchshij-uchitel-rodnogo-yazyka-i</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>598 000 ₽</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение интерактивной выставки дружба народов</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94473236-tender-organizaciya-i-provedenie-interaktivnoj-vystavki-drujba-narodov</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>311 167 ₽</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Тендер на услуги видеографа и видеомонтажера</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>/region/karachaevo-cherkesskaya-respublika/94452123-tender-uslugi-videografa-i-videomontajera</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>350 000 ₽</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото и видеосъемке и изготовлению видеороликов торжественного мероприятия день знаний в Краснодаре</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/krasnodar/94449122-tender-okazanie-uslug-po-foto-i-videosemke-i-izgotovleniyu-videorolikov-torjestvennogo-meropriyatiya-den-znanij</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>173 000 ₽</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Тендер на приобретение оборудования для фото- и видеосъемки</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/94430835-tender-priobretenie-oborudovaniya-dlya-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>327 360 ₽</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Тендер безопасность и оборудование для ее обеспечения.. фотоаппарат в Салавате</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/salavat/94432149-tender-bezopasnost-i-oborudovanie-dlya-ee-obespecheniya-fotoapparat</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>213 000 ₽</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению игры квн на кубок губернатора ленинградской области цикла региональных мероприятий в рамках поддержки квн ленинградской области</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/94424901-tender-okazanie-uslug-po-organizacii-i-provedeniyu-igry-kvn-na-kubok-gubernatora-leningradskoj-oblasti-cikla-regionalnyh-meropriyatij-v</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2 750 000 ₽</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Тендер на приобретение товаров для нужд воспитательной работы с осужденными в Шагонаре</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>/region/tyva-respublika/shagonar/94397498-tender-priobretenie-tovarov-dlya-nujd-vospitatelnoj-raboty-s-osujdennymi</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>77 999 ₽</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Тендер "оказание услуг по организации и проведению регионального мероприятия в рамках встречи участников проекта "путешествие мечты", проходящего в рамках всероссийского конкурса "большая перемена" в 2026 году в Красноярске</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/94411850-tender-okazanie-uslug-po-organizacii-i-provedeniyu-regionalnogo-meropriyatiya-v-ramkah-vstrechi-uchastnikov-proekta-puteshestvie</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2 397 386 ₽</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского семинар-совещания ведущих экспертов отдела реализации проектов и программ в сфере патриотического воспитания граждан управления реализации федеральных проектов и программ (муниципальных координаторов проекта "навигаторы детства") в Москве</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94363843-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-seminar-soveshchaniya-vedushchih-ekspertov-otdela-realizacii</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>112 071 520 ₽</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото - видеосъемке, изготовлению видеороликов для нужд предприятия тимашевские электрические сети филиала пао россети юг - кубаньэнерго в Тимашевске</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/timashevsk/94357258-tender-okazanie-uslug-po-foto-videosemke-izgotovleniyu-videorolikov-dlya-nujd-predpriyatiya-timashevskie-elektricheskie-seti</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>73 200 ₽</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеографа (съемка и монтаж) 8 видеороликов в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/94346260-tender-okazanie-uslug-videografa-semka-i-montaj-8-videorolikov</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>207 008 ₽</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по профессиональной видеосъёмке и фотосъемке мероприятия для участников и ветеранов сво, а также членов их семей в Казани</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/kazan/94336415-tender-okazanie-uslug-po-professionalnoj-videosemke-i-fotosemke-meropriyatiya-dlya-uchastnikov-i-veteranov-svo-a-takje-chlenov-ih</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по обеспечению видеосъемки и видеозаписи проведения дополнительного периода единого государственного экзамена в 2026 году в Орле</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>/region/orlovskaya-oblast/orel/94323818-tender-okazanie-uslugi-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-dopolnitelnogo-perioda-edinogo-gosudarstvennogo-ekzamena-v</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>354 999 ₽</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организацию и проведению фотосьемки в рамках организации и проведения форума работающей молодежи в Барнауле</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/barnaul/94324983-tender-okazanie-uslug-po-organizaciyu-i-provedeniyu-fotosemki-v-ramkah-organizacii-i-provedeniya-foruma-rabotayushchej-molodeji</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>40 000 ₽</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение адаптационного мероприятия "старт в профессию" для лиц, не прошедших государственную итоговую аттестацию по образовательным программам основного общего образования или получивших неудовлетворительные результаты в 2026 году и принятых на программы профессионального обучения в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94313756-tender-organizaciya-i-provedenie-adaptacionnogo-meropriyatiya-start-v-professiyu-dlya-lic-ne-proshedshih-gosudarstvennuyu-itogovuyu</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3 441 268 ₽</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому и программно-методическому обеспечению проведения стратегической проектировочной сессии с управленческими командами педагогических вузов (в рамках федерального проекта "педагоги и наставники" национального проекта "молодежь и дети") в Москве</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94531639-tender-okazanie-uslug-po-organizacionno-tehnicheskomu-i-programmno-metodicheskomu-obespecheniyu-provedeniya-strategicheskoj-proektirovochnoj-sessii</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>19 820 962 ₽</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъёмке концертов и торжественных мероприятий в рамках музыкального фестиваля, посвящённого 100?летию санкт?петербургского музыкального училища имени м.п.мусоргского и созданию итогового видеоролика и фильма в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94531888-tender-okazanie-uslug-po-videosemke-koncertov-i-torjestvennyh-meropriyatij-v-ramkah-muzykalnogo-festivalya-posvyashchennogo-100letiyu</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>198 000 ₽</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и изготовлению видеороликов в рамках проведения ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов в Уфе</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94505766-tender-okazanie-uslug-po-videosemke-i-izgotovleniyu-videorolikov-v-ramkah-provedeniya-ii-vserossijskoj-spartakiady-mejdu-subektami</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>360 000 ₽</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению церемонии награждения премии общественной палаты новосибирской области за вклад в развитие благотворительности и добровольчества новосибирской области "во благо" в Новосибирске</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>/region/novosibirskaya-oblast/novosibirsk/94501659-tender-okazanie-uslug-po-organizacii-i-provedeniyu-ceremonii-nagrajdeniya-premii-obshchestvennoj-palaty-novosibirskoj-oblasti</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>240 720 ₽</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации фотосъемки и видеосъемки всероссийского профессионального конкурса лучший учитель родного языка и родной литературы в 2026 году в Липецке</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>/region/lipeckaya-oblast/lipeck/94502505-tender-okazanie-uslug-po-organizacii-fotosemki-i-videosemki-vserossijskogo-professionalnogo-konkursa-luchshij-uchitel-rodnogo-yazyka-i</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>598 000 ₽</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение интерактивной выставки дружба народов</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94473236-tender-organizaciya-i-provedenie-interaktivnoj-vystavki-drujba-narodov</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>311 167 ₽</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Тендер на услуги видеографа и видеомонтажера</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>/region/karachaevo-cherkesskaya-respublika/94452123-tender-uslugi-videografa-i-videomontajera</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>350 000 ₽</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото и видеосъемке и изготовлению видеороликов торжественного мероприятия день знаний в Краснодаре</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/krasnodar/94449122-tender-okazanie-uslug-po-foto-i-videosemke-i-izgotovleniyu-videorolikov-torjestvennogo-meropriyatiya-den-znanij</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>173 000 ₽</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Тендер на приобретение оборудования для фото- и видеосъемки</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/94430835-tender-priobretenie-oborudovaniya-dlya-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>327 360 ₽</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Тендер безопасность и оборудование для ее обеспечения.. фотоаппарат в Салавате</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/salavat/94432149-tender-bezopasnost-i-oborudovanie-dlya-ee-obespecheniya-fotoapparat</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>213 000 ₽</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению игры квн на кубок губернатора ленинградской области цикла региональных мероприятий в рамках поддержки квн ленинградской области</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/94424901-tender-okazanie-uslug-po-organizacii-i-provedeniyu-igry-kvn-na-kubok-gubernatora-leningradskoj-oblasti-cikla-regionalnyh-meropriyatij-v</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2 750 000 ₽</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Тендер на приобретение товаров для нужд воспитательной работы с осужденными в Шагонаре</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>/region/tyva-respublika/shagonar/94397498-tender-priobretenie-tovarov-dlya-nujd-vospitatelnoj-raboty-s-osujdennymi</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>77 999 ₽</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Тендер "оказание услуг по организации и проведению регионального мероприятия в рамках встречи участников проекта "путешествие мечты", проходящего в рамках всероссийского конкурса "большая перемена" в 2026 году в Красноярске</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/94411850-tender-okazanie-uslug-po-organizacii-i-provedeniyu-regionalnogo-meropriyatiya-v-ramkah-vstrechi-uchastnikov-proekta-puteshestvie</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2 397 386 ₽</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского семинар-совещания ведущих экспертов отдела реализации проектов и программ в сфере патриотического воспитания граждан управления реализации федеральных проектов и программ (муниципальных координаторов проекта "навигаторы детства") в Москве</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94363843-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-seminar-soveshchaniya-vedushchih-ekspertov-otdela-realizacii</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>112 071 520 ₽</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото - видеосъемке, изготовлению видеороликов для нужд предприятия тимашевские электрические сети филиала пао россети юг - кубаньэнерго в Тимашевске</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/timashevsk/94357258-tender-okazanie-uslug-po-foto-videosemke-izgotovleniyu-videorolikov-dlya-nujd-predpriyatiya-timashevskie-elektricheskie-seti</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>73 200 ₽</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеографа (съемка и монтаж) 8 видеороликов в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/94346260-tender-okazanie-uslug-videografa-semka-i-montaj-8-videorolikov</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>207 008 ₽</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по профессиональной видеосъёмке и фотосъемке мероприятия для участников и ветеранов сво, а также членов их семей в Казани</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/kazan/94336415-tender-okazanie-uslug-po-professionalnoj-videosemke-i-fotosemke-meropriyatiya-dlya-uchastnikov-i-veteranov-svo-a-takje-chlenov-ih</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по обеспечению видеосъемки и видеозаписи проведения дополнительного периода единого государственного экзамена в 2026 году в Орле</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>/region/orlovskaya-oblast/orel/94323818-tender-okazanie-uslugi-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-dopolnitelnogo-perioda-edinogo-gosudarstvennogo-ekzamena-v</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>354 999 ₽</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организацию и проведению фотосьемки в рамках организации и проведения форума работающей молодежи в Барнауле</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/barnaul/94324983-tender-okazanie-uslug-po-organizaciyu-i-provedeniyu-fotosemki-v-ramkah-organizacii-i-provedeniya-foruma-rabotayushchej-molodeji</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>40 000 ₽</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение адаптационного мероприятия "старт в профессию" для лиц, не прошедших государственную итоговую аттестацию по образовательным программам основного общего образования или получивших неудовлетворительные результаты в 2026 году и принятых на программы профессионального обучения в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94313756-tender-organizaciya-i-provedenie-adaptacionnogo-meropriyatiya-start-v-professiyu-dlya-lic-ne-proshedshih-gosudarstvennuyu-itogovuyu</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3 441 268 ₽</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение карьерного мероприятия для студентов 1 курса спо введение в профессию в профессиональных образовательных организациях санкт-петербурга в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94313771-tender-organizaciya-i-provedenie-karernogo-meropriyatiya-dlya-studentov-1-kursa-spo-vvedenie-v-professiyu-v-professionalnyh-obrazovatelnyh</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3 564 395 ₽</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>/tender/94311296</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>7 557 600 ₽</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>/tender/94310999</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по созданию видеоконтента об участии делегации тюменской области в форуме молодёжи уральского федерального округа утро в Тюмени</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/tyumen/94304204-tender-uslugi-po-sozdaniyu-videokontenta-ob-uchastii-delegacii-tyumenskoj-oblasti-v-forume-molodeji-uralskogo-federalnogo-okruga-utro</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>167 500 ₽</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Тендер штатив для видеосъемки benro t691+mh2n в Бавлах</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/bavly/94300879-tender-shtativ-dlya-videosemki-benro-t691mh2n</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>4 500 ₽</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение балтийского форума соотечественников в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>/tender/94299020</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3 420 000 ₽</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>/tender/94291760</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>/tender/94291454</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Тендер демонтаж кингстонной решетки плавдока с видеосъемкой в Астрахани</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>/region/astrahanskaya-oblast/astrahan/94284615-tender-demontaj-kingstonnoj-reshetki-plavdoka-s-videosemkoj</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>262 500 ₽</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>/tender/94280747</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>/tender/94280712</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и изготовлению видеороликов в рамках проведения ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов в Уфе</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94279572-tender-okazanie-uslug-po-videosemke-i-izgotovleniyu-videorolikov-v-ramkah-provedeniya-ii-vserossijskoj-spartakiady-mejdu-subektami</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>360 000 ₽</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации уличного мероприятия огни залива в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94278809-tender-okazanie-uslug-po-organizacii-ulichnogo-meropriyatiya-ogni-zaliva</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>5 669 933 ₽</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Тендер на организацию мероприятий по развитию материально-технической базы государственной образовательной организации в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>/region/sverdlovskaya-oblast/ekaterinburg/94270807-tender-organizaciya-meropriyatij-po-razvitiyu-materialno-tehnicheskoj-bazy-gosudarstvennoj-obrazovatelnoj-organizacii</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>807 920 ₽</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по предоставлению платформы для видеосъемки в формате 360 и фотостойки в рамках мероприятия «обеспечение реализации торжественных мероприятий, посвященных 80-летию образования калининградской области, в муниципальных образованиях калининградской области» (день города ладушкина) в Калининграде</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>/region/kaliningradskaya-oblast/kaliningrad/94268388-tender-uslugi-po-predostavleniyu-platformy-dlya-videosemki-v-formate-360-i-fotostojki-v-ramkah-meropriyatiya-obespechenie</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по обеспечению видеосъемки и видеозаписи проведения дополнительного периода единого государственного экзамена в 2026 году в Орле</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>/region/orlovskaya-oblast/orel/94262092-tender-okazanie-uslugi-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-dopolnitelnogo-perioda-edinogo-gosudarstvennogo-ekzamena-v</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Тендер на услуги в области фото и видеосъемки</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/94260850-tender-uslugi-v-oblasti-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>22 000 ₽</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации репортажной фото- и видеосъемки с изготовлением отчетного видеоролика о проведении 48-й сессии межгосударственного совета по геодезии, картографии, кадастру и дистанционному зондированию земли государств – участников снг в 2026 году в Москве</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94251513-tender-okazanie-uslug-po-organizacii-reportajnoj-foto-i-videosemki-s-izgotovleniem-otchetnogo-videorolika-o-provedenii-48-j-sessii</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Тендер на закупку услуг по профессиональной видеосъемке и аудиозапись онлайн-курсов и высококачественный монтаж видеолекций онлайн-курсов в Москве</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94248963-tender-zakupka-uslug-po-professionalnoj-videosemke-i-audiozapis-onlajn-kursov-i-vysokokachestvennyj-montaj-videolekcij-onlajn-kursov</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>599 518 ₽</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению фото-/видеосъемки здания с использованием специального оборудования (в том числе для высотных работ) в Москве</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94242968-tender-okazanie-uslug-po-provedeniyu-foto-videosemki-zdaniya-s-ispolzovaniem-specialnogo-oborudovaniya-v-tom-chisle-dlya-vysotnyh-rabot</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению фото-/видеосъемки здания с использованием специального оборудования (в том числе для высотных работ) в Москве</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94243808-tender-okazanie-uslug-po-provedeniyu-foto-videosemki-zdaniya-s-ispolzovaniem-specialnogo-oborudovaniya-v-tom-chisle-dlya-vysotnyh-rabot</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение окружных форумов новая философия воспитания в Светлогорске</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>/tender/94223989</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>104 535 650 ₽</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг фотосъемки в рамках проведения ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов в Уфе</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94218751-tender-okazanie-uslug-fotosemki-v-ramkah-provedeniya-ii-vserossijskoj-spartakiady-mejdu-subektami-rossijskoj-federacii-po-letnim</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>264 000 ₽</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и фотосъемке, изготовление отчетного видеофильма по итогам реализации проекта российская национальная премия в сфере креативных индустрий в Москве</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94216604-tender-okazanie-uslug-po-videosemke-i-fotosemke-izgotovlenie-otchetnogo-videofilma-po-itogam-realizacii-proekta-rossijskaya-nacionalnaya-premiya-v</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Тендер на услуги btl мероприятий</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>/region/krym-respublika/94214403-tender-uslugi-btl-meropriyatij</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению фотосъемки по заданию заказчика на территории городского округа реутов в Реутове</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/reutov/94209050-tender-okazanie-uslug-po-provedeniyu-fotosemki-po-zadaniyu-zakazchika-na-territorii-gorodskogo-okruga-reutov</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по видеосъемке и монтажу научно-популярных подкастов (пр) в Якутске</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>/region/saha-yakutiya-respublika/yakutsk/94200293-tender-uslugi-po-videosemke-i-montaju-nauchno-populyarnyh-podkastov-pr</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>82 500 ₽</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Тендер на услуги в области фото и видеосъемки в Альметьевске</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/almetevsk/94195764-tender-uslugi-v-oblasti-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>20 000 ₽</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Тендер на услуги видеооператора в рамках проведения семинара феномен советского общепита. 1920 – 1930-е гг. в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94180120-tender-uslugi-videooperatora-v-ramkah-provedeniya-seminara-fenomen-sovetskogo-obshchepita-1920-1930-e-gg</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>21 000 ₽</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>09.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Тендер №kffzmu_228_разработка и создание нового видеоматериала "вводный инструктаж" на трех языках в связи с обновлением программы проведения вводного инструктажа, изменениями в структуре подразделении предприятия, а также необходимостью приведения видеоматериала в соответствие с актуальными требованиями охраны труда и промышленной безопасностью</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94155803-tender-kffzmu228razrabotka-i-sozdanie-novogo-videomateriala-vvodnyj-instruktaj-na-treh-yazykah-v-svyazi-s-obnovleniem-programmy-provedeniya-vvodnogo</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и фотосъемке, изготовление отчетного видеофильма по итогам реализации проекта российская национальная премия в сфере креативных индустрий в Москве</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94161141-tender-okazanie-uslug-po-videosemke-i-fotosemke-izgotovlenie-otchetnogo-videofilma-po-itogam-realizacii-proekta-rossijskaya-nacionalnaya-premiya-v</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации видеосъёмки с онлайн-трансляцией мероприятия, оказываемые в рамках комплекса услуг по реализации мероприятия и передать заказчику исключительные права на созданные в процессе оказания услуг результаты интеллектуальной деятельности</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94143153-tender-uslugi-po-organizacii-videosemki-s-onlajn-translyaciej-meropriyatiya-okazyvaemye-v-ramkah-kompleksa-uslug-po-realizacii-meropriyatiya-i</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по осуществлению звукозаписи, видеосъемки и предоставлению во временное пользование экрана в рамках проведения дня гатчинского муниципального округа</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/94131744-tender-okazanie-uslug-po-osushchestvleniyu-zvukozapisi-videosemki-i-predostavleniyu-vo-vremennoe-polzovanie-ekrana-v-ramkah-provedeniya</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>529 900 ₽</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Тендер фото на паспорт в Микуне</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>/region/komi-respublika/mikun/94107080-tender-foto-na-pasport</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>600 ₽</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Тендер на проведение патриотического форум-фестиваля россия начинается здесь (регистрационный номер: 903-а-гз) в Пскове</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>/region/pskovskaya-oblast/pskov/94082791-tender-provedenie-patrioticheskogo-forum-festivalya-rossiya-nachinaetsya-zdes-registracionnyj-nomer-903-a-gz</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>3 017 282 ₽</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъёмке и видеомонтажу творческих встреч согласно техническому заданию, с отчуждением исключительных прав в Вологде</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>/region/vologodskaya-oblast/vologda/94077325-tender-okazanie-uslug-po-videosemke-i-videomontaju-tvorcheskih-vstrech-soglasno-tehnicheskomu-zadaniyu-s-otchujdeniem-isklyuchitelnyh</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>52 666 ₽</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Тендер на закупку для ао русал менеджмент: услуги фото- и видеосъемки, производства видеороликов для центров спортивных единоборств сокол в 2026-2027 гг в Красноярске</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/94065743-tender-zakupka-dlya-ao-rusal-menedjment-uslugi-foto-i-videosemki-proizvodstva-videorolikov-dlya-centrov-sportivnyh-edinoborstv</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению финального этапа всероссийского патриотического форума "ступени поколений" в формате молодежного межмуниципального форума "область развития" в рамках реализации программы комплексного развития молодежной политики в ивановской области "регион для молодых" в Иваново</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>/region/ivanovskaya-oblast/ivanovo/94074839-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-finalnogo-etapa-vserossijskogo-patrioticheskogo-foruma-stupeni-pokolenij</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>680 000 ₽</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по созданию видеоконтента (цикла видео-подкастов) в Москве</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94057533-tender-okazanie-uslug-po-sozdaniyu-videokontenta-cikla-video-podkastov</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по фотосъемке городского праздника калуга – наш общий дом 21.08.2026 в городском парке культуры и отдыха в Калуге</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>/region/kalujskaya-oblast/kaluga/94039996-tender-okazanie-uslugi-po-fotosemke-gorodskogo-prazdnika-kaluga-nash-obshchij-dom-21082026-v-gorodskom-parke-kultury-i-otdyha</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение мероприятий. реклама. ритуальные услуги.. оказание услуг по видеосъемке и изготовлению видеороликов в рамках проведения спортивных соревнований по гребному слалому в рамках ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов без ограничений верхней границы возраста 2026 года "спартакиада народов россии" в Уфе</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94020329-tender-organizaciya-i-provedenie-meropriyatij-reklama-ritualnye-uslugi-okazanie-uslug-po-videosemke-i-izgotovleniyu-videorolikov-v</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>340 000 ₽</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по созданию видеоконтента (цикла видео-подкастов) в Москве</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94006543-tender-okazanie-uslug-po-sozdaniyu-videokontenta-cikla-video-podkastov</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению фото- и видеосъемки мероприятий проекта "нетрудные" в целях создания лаборатории промышленного дизайна в рамках реализации федерального проекта "регион для молодых" в Всеволожске</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/vsevolojsk/93999334-tender-okazanie-uslug-po-organizacii-i-provedeniyu-foto-i-videosemki-meropriyatij-proekta-netrudnye-v-celyah-sozdaniya</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>598 000 ₽</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по изготовлению сувенирной и полиграфической продукции, а также услуг по фото- и видеосъемке для участников проекта мобильные университетские смены скфо с наукой в села! в Махачкале</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>/region/dagestan-respublika/mahachkala/93998704-tender-okazanie-uslug-po-izgotovleniyu-suvenirnoj-i-poligraficheskoj-produkcii-a-takje-uslug-po-foto-i-videosemke-dlya-uchastnikov</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1 100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению фотосьемки инклюзивного добровольческого фестиваля добрые люди в Барнауле</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/barnaul/93993934-tender-okazanie-uslug-po-organizacii-i-provedeniyu-fotosemki-inklyuzivnogo-dobrovolcheskogo-festivalya-dobrye-lyudi</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>20 000 ₽</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение мероприятий. реклама. ритуальные услуги.. услуги по видеосъемке и изготовлению видео ролика в рамках проведения спортивных соревнований по велосипедному спорту в рамках ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов без ограничения верхней границы возраста 2026 года в Уфе</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/93978264-tender-organizaciya-i-provedenie-meropriyatij-reklama-ritualnye-uslugi-uslugi-po-videosemke-i-izgotovleniyu-video-rolika-v-ramkah</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>200 000 ₽</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>26.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Тендер на организацию фото- и видеосъёмки в рамках мероприятий для участников проекта медиакласс в московской школе в Москве</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93977257-tender-organizaciya-foto-i-videosemki-v-ramkah-meropriyatij-dlya-uchastnikov-proekta-mediaklass-v-moskovskoj-shkole</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>718 340 ₽</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации и проведению фото- и видеосъемки мероприятия в целях проведения обучающей программы "мама-предприниматель" в Томске</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>/region/tomskaya-oblast/tomsk/93974481-tender-uslugi-po-organizacii-i-provedeniyu-foto-i-videosemki-meropriyatiya-v-celyah-provedeniya-obuchayushchej-programmy-mama</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>53 450 ₽</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг фотографа в рамках проведения второго этапа турнира совета работающей молодёжи алтайского края битва советов в Барнауле</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/barnaul/93967978-tender-okazanie-uslug-fotografa-v-ramkah-provedeniya-vtorogo-etapa-turnira-soveta-rabotayushchej-molodeji-altajskogo-kraya-bitva-sovetov</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>10 000 ₽</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Тендер видеосъемка производства и мероприятия с подготовкой фото- и видеоматериалов в Рязани</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>/region/ryazanskaya-oblast/ryazan/93962872-tender-videosemka-proizvodstva-i-meropriyatiya-s-podgotovkoj-foto-i-videomaterialov</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации экспозиции санкт-петербурга в рамках международной выставки-ярмарки агрорусь в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93936502-tender-okazanie-uslug-po-organizacii-ekspozicii-sankt-peterburga-v-ramkah-mejdunarodnoj-vystavki-yarmarki-agrorus</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>9 825 500 ₽</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по фото, видеосъемке, изготовлению видеографики, организации видеотрансляций и монтажу видеосюжетов о деятельности пао "россети московский регион" для нужд пао "россети московский регион"</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93920166-tender-okazanie-kompleksa-uslug-po-foto-videosemke-izgotovleniyu-videografiki-organizacii-videotranslyacij-i-montaju-videosyujetov-o-deyatelnosti</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>42 128 172 ₽</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по созданию и монтажу видеоролика в Перми</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/perm/93926204-tender-vypolnenie-rabot-po-sozdaniyu-i-montaju-videorolika</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>84 333 ₽</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по созданию и монтажу видеоролика в Перми</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/perm/93926203-tender-vypolnenie-rabot-po-sozdaniyu-i-montaju-videorolika</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>84 333 ₽</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по информационному сопровождению (фотосъемка, репортажи, публикации в "дневнике смены" и социальных сетях) работы съемочных групп в рамках киносмены; участие в проведении кастинга и кинопроб (фото- и видеосъемка кандидатов); работа в качестве помощника оператора и монтажера, участие в проведении тематических мероприятий киносмены: "корпорация rosson 2.0"</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/93918118-tender-uslugi-po-informacionnomu-soprovojdeniyu-fotosemka-reportaji-publikacii-v-dnevnike-smeny-i-socialnyh-setyah-raboty-semochnyh-grupp-v</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>14 942 ₽</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению семинара для представителей военно-патриотических клубов в рамках всероссийского проекта диалоги с героями</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/93916554-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-seminara-dlya-predstavitelej-voenno-patrioticheskih-klubov-v-ramkah-vserossijskogo</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>15 830 000 ₽</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по созданию видеоконтента в рамках организации и проведения театрализованной программы рождение земли югорской в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/93911365-tender-okazanie-uslugi-po-sozdaniyu-videokontenta-v-ramkah-organizacii-i-provedeniya</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>85 000 ₽</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>/region/sverdlovskaya-oblast/93894808-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-videosemki-iili-pryamoj-onlajn-videotranslyacii-v-ramkah-integracii-rossijskogo</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по обеспечению оборудованием в целях организации второго международного фестиваля традиционного и современного этнического творчества "абашевские узоры", разработка светового дизайна и трехмерной модели площадки фестиваля, услуги видеосъемки и онлайн-трансляции в Пензе</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>/region/penzenskaya-oblast/penza/93894935-tender-uslugi-po-obespecheniyu-oborudovaniem-v-celyah-organizacii-vtorogo-mejdunarodnogo-festivalya-tradicionnogo-i-sovremennogo</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>15 126 400 ₽</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>/region/sverdlovskaya-oblast/ekaterinburg/93894403-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-videosemki-iili-pryamoj-onlajn-videotranslyacii-v-ramkah</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по фото-и видеосъёмке и изготовлению видеороликов в Владимире</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>/region/vladimirskaya-oblast/vladimir/93891819-tender-uslugi-po-foto-i-videosemke-i-izgotovleniyu-videorolikov</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>498 980 ₽</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по подготовке и проведению, видеосъёмке и созданию видеороликов, организации и оформлению выставочной композиции мероприятия туристической (событийной) направленности "семейный гастрономический фестиваль "деньпельмень" в 2026 году в Комсомольске-на-Амуре</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>/region/habarovskij-kraj/komsomolsk-na-amure/93868543-tender-okazanie-uslug-po-podgotovke-i-provedeniyu-videosemke-i-sozdaniyu-videorolikov-organizacii-i-oformleniyu-vystavochnoj</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>290 276 ₽</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского семинар-совещания главных экспертов отдела реализации проектов и программ в сфере патриотического воспитания граждан управления реализации федеральных проектов и программ (региональных координаторов проекта "навигаторы детства") и главного эксперта отдела международного сотрудничества (республиканского координатора проекта "навигаторы детства республики южная осетия")</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/93855307-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-seminar-soveshchaniya-glavnyh-ekspertov-otdela-realizacii</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>8 283 770 ₽</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Тендер выбор контрагента по оказанию услуг проведения фото-видеосъемки (предпродакшен, продакшен, постпродакшен) для гостиничного оператора cosmos hotel group в Москве</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93827139-tender-vybor-kontragenta-po-okazaniyu-uslug-provedeniya-foto-videosemki-predprodakshen-prodakshen-postprodakshen-dlya-gostinichnogo-operatora-cosmos</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение молодежно-патриотических мероприятий для подростков "не гаснет памяти огонь", проживающих на территории внутригородского муниципального образования города федерального значения санкт-петербурга поселок шушары в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93807259-tender-organizaciya-i-provedenie-molodejno-patrioticheskih-meropriyatij-dlya-podrostkov-ne-gasnet-pamyati-ogon-projivayushchih-na</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>750 000 ₽</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации нанесения мурала симбирская чебурашка в рамках мероприятия, связанного с участием в фестивале уличного искусства приволжского федерального округа формарт в Ульяновске</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>/region/ulyanovskaya-oblast/ulyanovsk/93807017-tender-uslugi-po-organizacii-naneseniya-murala-simbirskaya-cheburashka-v-ramkah-meropriyatiya-svyazannogo-s-uchastiem-v-festivale</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>589 500 ₽</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>18.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по созданию видеоконтента в рамках организации и проведения торжественных мероприятий , посвященных празднованию дня работников нефтяной и газовой промышленности в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/93805171-tender-okazanie-uslugi-po-sozdaniyu-videokontenta-v-ramkah-organizacii-i-provedeniya</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>336 000 ₽</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по созданию видеоконтента в рамках организации и проведения концерта "классика без границ" в исполнении концертного духового оркестра югры и солиста большого театра россии эльчина азизова в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>/tender/93805167</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>162 333 ₽</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение мероприятий. реклама. ритуальные услуги.. оказание услуг по видеосъемке и изготовлению видео ролика при проведении спортивных соревнований по триатлону в рамках ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов без ограничения верхней границы возраста 2026 года (далее мероприятия) в Уфе</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/93791832-tender-organizaciya-i-provedenie-meropriyatij-reklama-ritualnye-uslugi-okazanie-uslug-po-videosemke-i-izgotovleniyu-video-rolika-pri</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>260 000 ₽</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по организации и проведению семейного мероприятия для сотрудников в Химках</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/himki/93781566-tender-okazanie-uslugi-po-organizacii-i-provedeniyu-semejnogo-meropriyatiya-dlya-sotrudnikov</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по организации и проведению семейного мероприятия для сотрудников в Химках</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/himki/93779064-tender-okazanie-uslugi-po-organizacii-i-provedeniyu-semejnogo-meropriyatiya-dlya-sotrudnikov</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение мероприятий. реклама. ритуальные услуги.. оказание услуг по видеосъемке и изготовлению видео ролика при проведении спортивных соревнований по триатлону в рамках ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов без ограничения верхней границы возраста 2026 года (далее мероприятия) в Уфе</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/93759923-tender-organizaciya-i-provedenie-meropriyatij-reklama-ritualnye-uslugi-okazanie-uslug-po-videosemke-i-izgotovleniyu-video-rolika-pri</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>260 000 ₽</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>16.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по проведению фотосъемки для филиала ириклинская грэс ао интер рао - электрогенерация</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>/region/orenburgskaya-oblast/93735366-tender-uslugi-po-provedeniyu-fotosemki-dlya-filiala-iriklinskaya-gres-ao-inter-rao-elektrogeneraciya</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>65 000 ₽</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению мероприятия семинар-совещание для сотрудников региональных органов власти в рамках реализации конкурса росмолодёжь.гранты в Смоленске</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>/region/smolenskaya-oblast/smolensk/93727927-tender-okazanie-uslug-po-organizacii-i-provedeniyu-meropriyatiya-seminar-soveshchanie-dlya-sotrudnikov-regionalnyh-organov-vlasti-v</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>5 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение научно-методической конференции воспитание созиданием в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93727458-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-nauchno-metodicheskoj-konferencii-vospitanie-sozidaniem</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>9 854 722 ₽</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>21.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению семейного мероприятия для сотрудников в Москве</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93720914-tender-okazanie-uslug-po-organizacii-i-provedeniyu-semejnogo-meropriyatiya-dlya-sotrudnikov</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>16.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Тендер фото на паспорт в Микуне</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>/region/komi-respublika/mikun/93722704-tender-foto-na-pasport</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>600 ₽</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению фото- и (или) видеосъемки по заказу избирательной комиссии ростовской области в Ростове-на-Дону</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>/region/rostovskaya-oblast/rostov-na-donu/93658683-tender-okazanie-uslug-po-obespecheniyu-foto-i-ili-videosemki-po-zakazu-izbiratelnoj-komissii-rostovskoj-oblasti</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению церемонии закрытия региональных этапов чемпионата профессионалов в 2026 г. на полигоне приволжской железной дороги в Энгельсе</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>/region/saratovskaya-oblast/engels/93669949-tender-okazanie-uslug-po-provedeniyu-ceremonii-zakrytiya-regionalnyh-etapov-chempionata-professionalov-v-2026-g-na-poligone</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>1 108 583 ₽</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Тендер предметная видеосъёмка (мониторинг) в Красногорске</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/krasnogorsk/93659828-tender-predmetnaya-videosemka-monitoring</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского фестиваля детского творчества вдохновленные детством в Москве</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93667673-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-festivalya-detskogo-tvorchestva-vdohnovlennye-detstvom</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>9 527 509 ₽</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение досуговых мероприятий для жителей внутригородского муниципального образования города федерального значения санкт-петербурга поселок шушары</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93665784-tender-organizaciya-i-provedenie-dosugovyh-meropriyatij-dlya-jitelej-vnutrigorodskogo-municipalnogo-obrazovaniya-goroda-federalnogo</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>948 989 ₽</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Тендер на изготовление видеоролика с использованием квадрокоптера (с прошивкой для возможности использования над водой) в течение 2-х полных дней (зерновой терминал г. азов) в Азове</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>/region/rostovskaya-oblast/azov/93665496-tender-izgotovlenie-videorolika-s-ispolzovaniem-kvadrokoptera-s-proshivkoj-dlya-vozmojnosti-ispolzovaniya-nad-vodoj-v-techenie-2-h-polnyh</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Тендер цифровая техника, прочее, устройства запоминающие внешние, ip оборудование, фото/видео техника/оптика и оборудование, видеокамеры в Анапе</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/anapa/93660949-tender-cifrovaya-tehnika-prochee-ustrojstva-zapominayushchie-vneshnie-ip-oborudovanie-fotovideo-tehnikaoptika-i-oborudovanie-videokamery</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>164 829 ₽</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по проведению видеосъемки, трансляции в интернет и на средства видеоотображения коллективного мероприятия в городах рф в Москве</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>/tender/93644172</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Тендер услуга по техническому и программному обеспечению видеосъемки проведения специализированного клинического интервью по стандартизированной операционной процедуре проведения этологического исследования с использованием биометрической видеорегистрации</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93637060-tender-usluga-po-tehnicheskomu-i-programmnomu-obespecheniyu-videosemki-provedeniya-specializirovannogo-klinicheskogo-intervyu-po</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по проведению видеосъемки и монтажу видеороликов для нужд администрации муниципального образования апшеронский район в Апшеронске</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/apsheronsk/93635751-tender-uslugi-po-provedeniyu-videosemki-i-montaju-videorolikov-dlya-nujd-administracii-municipalnogo-obrazovaniya-apsheronskij</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>449 800 ₽</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение военно-тактической игры для подростков внутригородского муниципального образования города федерального значения санкт-петербурга поселок шушары</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93614334-tender-organizaciya-i-provedenie-voenno-takticheskoj-igry-dlya-podrostkov-vnutrigorodskogo-municipalnogo-obrazovaniya-goroda-federalnogo</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>610 050 ₽</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению мероприятий "россия - родина моя" и "слава россии" для жителей внутригородского муниципального образования города федерального значения санкт-петербурга поселок шушары</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93614108-tender-okazanie-uslug-po-organizacii-i-provedeniyu-meropriyatij-rossiya-rodina-moya-i-slava-rossii-dlya-jitelej-vnutrigorodskogo</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>493 867 ₽</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Тендер на услуги в области фото и видеосъемки в Нижнекамске</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/nijnekamsk/93606985-tender-uslugi-v-oblasti-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>200 ₽</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению церемонии закрытия региональных этапов чемпионата профессионалов в 2026 г. на полигоне приволжской железной дороги в Энгельсе</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>/region/saratovskaya-oblast/engels/93603975-tender-okazanie-uslug-po-provedeniyu-ceremonii-zakrytiya-regionalnyh-etapov-chempionata-professionalov-v-2026-g-na-poligone</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>1 108 583 ₽</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеосъёмки и монтаж мультимедийного проекта в Кургане</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>/region/kurganskaya-oblast/kurgan/93594523-tender-okazanie-uslug-videosemki-i-montaj-multimedijnogo-proekta</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>30 000 ₽</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Тендер услуг по видеосъемке строящихся и готовых объектов, курируемых министерством строительства кузбасса</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>/region/kemerovskaya-oblast/93587797-tender-uslug-po-videosemke-stroyashchihsya-i-gotovyh-obektov-kuriruemyh-ministerstvom-stroitelstva-kuzbassa</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>162 000 ₽</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъемки и монтажу короткометражного фильма в Сургуте</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/surgut/93559703-tender-okazanie-uslug-po-organizacii-videosemki-i-montaju-korotkometrajnogo-filma</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации всероссийского форума пик возможностей в Москве</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93557243-tender-okazanie-kompleksa-uslug-po-organizacii-vserossijskogo-foruma-pik-vozmojnostej</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по сопровождению открытого корпоративного чемпионата профессионального мастерства группы компаний "россети" по стандартам автономной некоммерческой организации "агентство развития профессионального мастерства (ворлдскиллс россия)", по компетенции "техническое обслуживание и ремонт распределительных сетей 0,4-20кв" с организацией видеосъёмки и созданием видеороликов для нужд филиала пао "россети юг" - "кубаньэнерго" в Краснодаре</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/krasnodar/93555140-tender-okazanie-uslug-po-soprovojdeniyu-otkrytogo-korporativnogo-chempionata-professionalnogo-masterstva-gruppy-kompanij-rosseti-po</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>472 140 ₽</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по монтажу видеороликов по материалам заказчика в Москве</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93551119-tender-okazanie-uslug-po-montaju-videorolikov-po-materialam-zakazchika</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>1 359 803 ₽</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по удалению сточных отходов (жбо) для нужд казенного учреждения ханты-мансийского автономного округа – югры центроспас-югория</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/93545668-tender-okazanie-uslug-po-udaleniyu-stochnyh-othodov-jbo-dlya-nujd-kazennogo-uchrejdeniya-hanty</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по фото- и видеосъемке и изготовлению видеоконтента для нужд филиала пао россети центр и приволжье – удмуртэнерго</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>/region/udmurtskaya-respublika/93522636-tender-uslugi-po-foto-i-videosemke-i-izgotovleniyu-videokontenta-dlya-nujd-filiala-pao-rosseti-centr-i-privolje-udmurtenergo</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>349 999 ₽</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по обследованию лэп с применением беспилотных авиационных систем для нужд филиала пао россети - ленинградское пмэс</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93511067-tender-vypolnenie-rabot-po-obsledovaniyu-lep-s-primeneniem-bespilotnyh-aviacionnyh-sistem-dlya-nujd-filiala-pao-rosseti-leningradskoe-pmes</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>4 615 619 ₽</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению всероссийского патриотического форума в Москве</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93524691-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-vserossijskogo-patrioticheskogo-foruma</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>77 567 000 ₽</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению финала всероссийского конкурса наставников быть, а не казаться</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>/region/tulskaya-oblast/93524611-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-finala-vserossijskogo-konkursa-nastavnikov-byt-a-ne-kazatsya</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>132 617 000 ₽</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Тендер комплекс услуг по организации и проведению краевого инфраструктурного проекта тим юниор – 2026 в Красноярске</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/93515889-tender-kompleks-uslug-po-organizacii-i-provedeniyu-kraevogo-infrastrukturnogo-proekta-tim-yunior-2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>7 466 230 ₽</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Тендер на услуги фото- и видеосъемки x международного фестиваля любительских и независимых театров "театральная пестрядь", профессиональной обработки фото и видеоматериала, изготовленных в период проведения фестиваля</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/93504233-tender-uslugi-foto-i-videosemki-x-mejdunarodnogo-festivalya-lyubitelskih-i-nezavisimyh-teatrov-teatralnaya-pestryad-professionalnoj-obrabotki-foto</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>50 000 ₽</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению гражданского форума новосибирской области "гражданский диалог" для представителей социально ориентированных некоммерческих организаций новосибирской области в сфере общественных инициатив и развития институтов гражданского общества в Новосибирске</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>/region/novosibirskaya-oblast/novosibirsk/93489373-tender-okazanie-uslug-po-provedeniyu-grajdanskogo-foruma-novosibirskoj-oblasti-grajdanskij-dialog-dlya-predstavitelej-socialno</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2 910 776 ₽</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъемки и монтажу короткометражного фильма в Сургуте</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/surgut/93490243-tender-okazanie-uslug-po-organizacii-videosemki-i-montaju-korotkometrajnogo-filma</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъемки и монтажу короткометражного фильма в Сургуте</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/surgut/93480999-tender-okazanie-uslug-po-organizacii-videosemki-i-montaju-korotkometrajnogo-filma</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по видеосъемке спектаклей из репертуара и мероприятий заказчика на сцене твой молодёжный театр в Перми</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/perm/93477992-tender-uslugi-po-videosemke-spektaklej-iz-repertuara-i-meropriyatij-zakazchika-na-scene-tvoj-molodejnyj-teatr</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>95 500 ₽</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение фото- и видеосъемки мероприятия заказчика 10.07.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93467294-tender-organizaciya-i-provedenie-foto-i-videosemki-meropriyatiya-zakazchika-10072026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>56 333 ₽</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению регионального туристического слета первый горный в красноярском крае в 2026 году</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/93464777-tender-okazanie-uslug-po-organizacii-i-provedeniyu-regionalnogo-turisticheskogo-sleta-pervyj-gornyj-v-krasnoyarskom-krae-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2 872 898 ₽</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Тендер на закупку товара: экшн-камера, карта памяти, прожекторы в Козловке</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>/region/chuvashskaya---chuvashiya-respublika/kozlovka/93414365-tender-zakupka-tovara-ekshn-kamera-karta-pamyati-projektory</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>48 895 ₽</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по организации и проведению фото- и видеосъемки мероприятия в рамках проведения iv межрегионального форума «бизнес от сердца» в Томске</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>/region/tomskaya-oblast/tomsk/93410940-tender-okazanie-uslugi-po-organizacii-i-provedeniyu-foto-i-videosemki-meropriyatiya-v-ramkah-provedeniya-iv-mejregionalnogo-foruma-biznes</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>66 050 ₽</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению фото- видеосъемки здания в Москве</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93410652-tender-okazanie-uslug-po-provedeniyu-foto-videosemki-zdaniya</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке спектакля жестокие игры для нужд спб гбук театр юных зрителей им. а.а. брянцева в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93394067-tender-okazanie-uslug-po-videosemke-spektaklya-jestokie-igry-dlya-nujd-spb-gbuk-teatr-yunyh-zritelej-im-aa-bryanceva</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>32 700 ₽</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по дистанционному мониторингу водных объектов хабаровского края для противодействия незаконному вылову водных биоресурсов с использованием беспилотной авиационной системы (бас) отечественного производства</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>/region/habarovskij-kraj/93385843-tender-uslugi-po-distancionnomu-monitoringu-vodnyh-obektov-habarovskogo-kraya-dlya-protivodejstviya-nezakonnomu-vylovu-vodnyh-bioresursov-s</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>79 870 ₽</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фотосъемке и видеосъёмке изготовлению готового видеоролика, связанного с производством и возведением модульного дома на период июль 2026г - апрель 2027г в Наро-Фоминске</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>/tender/93313387</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фотосъемке и видеосъёмке строительства объекта восточное бутово к.43.1, изготовлению готового видеоролика, связанного с производством и возведением модульного дома в Наро-Фоминске</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/naro-fominsk/93311528-tender-okazanie-uslug-po-fotosemke-i-videosemke-stroitelstva-obekta-vostochnoe-butovo-k431-izgotovleniyu-gotovogo-videorolika</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по очистке и телеинспекции канализационных систем в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93290728-tender-okazanie-uslug-po-ochistke-i-teleinspekcii-kanalizacionnyh-sistem</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>334 285 ₽</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение тренинговой программы навигаторы детства: искусство быть наставником в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93281515-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-treningovoj-programmy-navigatory-detstva-iskusstvo-byt-nastavnikom</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>11 025 945 ₽</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по подготовке и проведению мероприятия союзного государства слет юных экологов беларуси и россии экология без границ в 2026 году в Смоленске</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>/region/smolenskaya-oblast/smolensk/93248990-tender-okazanie-uslug-po-podgotovke-i-provedeniyu-meropriyatiya-soyuznogo-gosudarstva-slet-yunyh-ekologov-belarusi-i-rossii-ekologiya</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>4 020 774 ₽</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке спектакля жестокие игры для нужд спб гбук театр юных зрителей им. а.а. брянцева в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93233969-tender-okazanie-uslug-po-videosemke-spektaklya-jestokie-igry-dlya-nujd-spb-gbuk-teatr-yunyh-zritelej-im-aa-bryanceva</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>32 700 ₽</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Тендер фото на паспорт в Микуне</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>/region/komi-respublika/mikun/93221372-tender-foto-na-pasport</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>600 ₽</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>25.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению техникой и стендов наглядной агитации для нужд фку ик-5 уфсин россии по рязанской области</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>/region/ryazanskaya-oblast/93221284-tender-okazanie-uslug-po-obespecheniyu-tehnikoj-i-stendov-naglyadnoj-agitacii-dlya-nujd-fku-ik-5-ufsin-rossii-po-ryazanskoj-oblasti</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>316 000 ₽</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>25.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и созданию пилотного виртуального ролика (2-й этап торгов)</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>/region/irkutskaya-oblast/93218717-tender-okazanie-uslug-po-videosemke-i-sozdaniyu-pilotnogo-virtualnogo-rolika-2-j-etap-torgov</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видео-сопровождения для реализации мероприятий, направленных на развитие общероссийского движения детей и молодежи движение первых по направлению деятельности рддм</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>/region/kaliningradskaya-oblast/93210698-tender-okazanie-uslug-video-soprovojdeniya-dlya-realizacii-meropriyatij-napravlennyh-na-razvitie-obshcherossijskogo-dvijeniya-detej-i</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>400 000 ₽</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по изготовлению видеопродукции для нужд ооо "хк "нефтехимик" в Нижнекамске</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/nijnekamsk/93213388-tender-okazanie-uslug-po-izgotovleniyu-videoprodukcii-dlya-nujd-ooo-hk-neftehimik</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Тендер на проведение фото и видеосъемки медицинских центров в Москве</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93206458-tender-provedenie-foto-i-videosemki-medicinskih-centrov</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по проектированию, монтажу и пусконаладке интерактивных диспетчерских центров оперативно-диспетчерской службы ао ск алтайкрайэнерго</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/93195985-tender-vypolnenie-rabot-po-proektirovaniyu-montaju-i-puskonaladke-interaktivnyh-dispetcherskih-centrov-operativno-dispetcherskoj-slujby-ao-sk</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Тендер оборудование для фото и видеосъемки в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/93194467-tender-oborudovanie-dlya-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Тендер оборудование для фото и видеосъемки в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/93193749-tender-oborudovanie-dlya-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению курсов повышения квалификации для специалистов профильных ведомств в республике конго (в рамках реализации федерального проекта "санитарный щит")</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>/region/saratovskaya-oblast/93189670-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-kursov-povysheniya-kvalifikacii-dlya-specialistov-profilnyh-vedomstv-v</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>4 977 000 ₽</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению курсов повышения квалификации для специалистов профильных ведомств в боливарианской республике венесуэла (в рамках реализации федерального проекта "санитарный щит")</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>/region/saratovskaya-oblast/93189671-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-kursov-povysheniya-kvalifikacii-dlya-specialistov-profilnyh-vedomstv-v</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2 990 050 ₽</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке с созданием видеоролика мероприятия ночь в дивногорье в Воронеже</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>/region/voronejskaya-oblast/voronej/93193261-tender-okazanie-uslug-po-videosemke-s-sozdaniem-videorolika-meropriyatiya-noch-v-divnogore</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>55 000 ₽</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Тендер (требуется обеспечение исполнения договора 30% от нмдц) оказание услуг по организации проведения мероприятия всероссийская ярмарка трудоустройства в Москве</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93190077-tender-trebuetsya-obespechenie-ispolneniya-dogovora-30-ot-nmdc-okazanie-uslug-po-organizacii-provedeniya-meropriyatiya-vserossijskaya-yarmarka</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>889 600 ₽</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому обеспечению мероприятия (региональные финалы) по развитию молодежного предпринимательства "я в деле" (в части обеспечения питания, питьевого режима, фото и видеосъемки, типографской продукцией), направленного на повышение компетенции наставников в 2026 году</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>/tender/93182206</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>22.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Тендер профессиональный квадрокоптер для видеосъёмки в Донецке</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>/region/donetskaya-narodnaya-respublika/donetsk/93177471-tender-professionalnyj-kvadrokopter-dlya-videosemki</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>95 250 ₽</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Тендер фото- и видеосъемке мероприятий первого межрегионального фестиваля моноспектаклей я — не я в Чайковском</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/chajkovskij/93159415-tender-foto-i-videosemke-meropriyatij-pervogo-mejregionalnogo-festivalya-monospektaklej-ya-ne-ya</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>110 552 ₽</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Тендер фото- и видеосъемке мероприятий первого межрегионального фестиваля моноспектаклей я — не я в Чайковском</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/chajkovskij/93155851-tender-foto-i-videosemke-meropriyatij-pervogo-mejregionalnogo-festivalya-monospektaklej-ya-ne-ya</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>110 552 ₽</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Тендер эа-№-11143/26 услуги по изготовлению знаков (наклеек) противопожарной безопасности в Красноярске</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/93151595-tender-ea-1114326-uslugi-po-izgotovleniyu-znakov-nakleek-protivopojarnoj-bezopasnosti</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>39 617 ₽</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского семинар-совещания для дистанционных работников отдела реализации проектов и программ в сфере патриотического воспитания граждан управления реализации федеральных проектов и программ, дистанционных работников отдела международного сотрудничества и специалистов по документационному обеспечению персонала управления по работе с персоналом дистанционного режима работы в Москве</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93148552-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-seminar-soveshchaniya-dlya-distancionnyh-rabotnikov-otdela</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>31 214 550 ₽</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото-и видеосъемке и изготовлению видеоконтента для нужд филиала пао россети центр и приволжье – удмуртэнерго в Ижевске</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>/region/udmurtskaya-respublika/ijevsk/93121000-tender-okazanie-uslug-po-foto-i-videosemke-i-izgotovleniyu-videokontenta-dlya-nujd-filiala-pao-rosseti-centr-i-privolje</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>349 999 ₽</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг профессиональной видеосъемки для нужд пао красноярскэнергосбыт в Красноярске</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/93130573-tender-okazanie-uslug-professionalnoj-videosemki-dlya-nujd-pao-krasnoyarskenergosbyt</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>499 900 ₽</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации подготовки и проведению фото- и аэросъемки в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93124548-tender-okazanie-uslug-po-organizacii-podgotovki-i-provedeniyu-foto-i-aerosemki</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Тендер как представитель "пермской официальной лиги квн" на территории пермского края согласно договора __________________, принимает на себя обязательства оказать услуги по подготовке, организации и проведению мероприятия "чемпионат квн" в Перми</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/perm/93119242-tender-kak-predstavitel-permskoj-oficialnoj-ligi-kvn-na-territorii-permskogo-kraya-soglasno-dogovora-prinimaet-na-sebya-obyazatelstva-okazat</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>600 000 ₽</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по формированию культурно - образовательного пространства в Люберцах</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/lyubercy/93097678-tender-okazanie-uslug-po-formirovaniyu-kulturno-obrazovatelnogo-prostranstva</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Тендер (требуется обеспечение исполнения договора 30% от нмдц) оказание услуг по организации проведения мероприятия всероссийская ярмарка трудоустройства в Москве</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93088510-tender-trebuetsya-obespechenie-ispolneniya-dogovora-30-ot-nmdc-okazanie-uslug-po-organizacii-provedeniya-meropriyatiya-vserossijskaya-yarmarka</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>518 250 ₽</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации фото - видео сопровождения корпоративных мероприятий ооо ук "металлоинвест" на территории присутствия предприятий заказчика в формате фотосъемки, видеосъемки, создания 2d и 3d графики в Москве</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93080800-tender-okazanie-uslug-po-organizacii-foto-video-soprovojdeniya-korporativnyh-meropriyatij-ooo-uk-metalloinvest-na-territorii-prisutstviya</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>22.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по видеосъемке процессов и результатов производственной деятельности ао россети тюмень, в том числе с использованием аэротехники</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>/tender/93073609</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>499 895 ₽</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского форума пространство воспитания: диалог, традиции, единство в Москве</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93039854-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-foruma-prostranstvo-vospitaniya-dialog-tradicii-edinstvo</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>6 405 609 ₽</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по видеосъемке основных событий жизни университета (заказчика) с размещением в еженедельной телепрограмме, освещающей события, происходящие в санкт-петербурге в 2026 году в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93035791-tender-uslugi-po-videosemke-osnovnyh-sobytij-jizni-universiteta-zakazchika-s-razmeshcheniem-v-ejenedelnoj-teleprogramme-osveshchayushchej</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>95 000 ₽</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Тендер на создание фотобанка и видеоролика</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>/region/novosibirskaya-oblast/93033101-tender-sozdanie-fotobanka-i-videorolika</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>50 000 ₽</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Тендер видеосъёмка курьеров в Москве</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93014440-tender-videosemka-kurerov</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>22.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению полуфинала всероссийского конкурса наставников быть, а не казаться для центрального и северо-западного федеральных округов в Суздале</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>/region/vladimirskaya-oblast/suzdal/93014253-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-polufinala-vserossijskogo-konkursa-nastavnikov-byt-a-ne-kazatsya-dlya</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>24 967 000 ₽</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому обеспечению мероприятия (региональные финалы) по развитию молодежного предпринимательства "я в деле" (в части обеспечения питания, питьевого режима, фото и видеосъемки и типографской продукцией), направленного на повышение компетенции наставников в 2026 году в Иркутске</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>/tender/93008352</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по организации и проведению торжественного вручения дипломов выпускникам в Москве</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93004743-tender-okazanie-uslugi-po-organizacii-i-provedeniyu-torjestvennogo-vrucheniya-diplomov-vypusknikam</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>516 720 ₽</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому обеспечению мероприятия (региональные финалы) по развитию молодежного предпринимательства "я в деле" (в части обеспечения питания, питьевого режима, фото и видеосъемки и типографской продукцией), направленного на повышение компетенции наставников в 2026 году</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>/tender/93002897</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по оказанию фото и видеосъемки</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/92991568-tender-uslugi-po-okazaniyu-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Тендер фото на паспорт в Микуне</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>/region/komi-respublika/mikun/92990243-tender-foto-na-pasport</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>300 ₽</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению техникой и стендов наглядной агитации для нужд фку ик-5 уфсин россии по рязанской области</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>/region/ryazanskaya-oblast/92986914-tender-okazanie-uslug-po-obespecheniyu-tehnikoj-i-stendov-naglyadnoj-agitacii-dlya-nujd-fku-ik-5-ufsin-rossii-po-ryazanskoj-oblasti</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>316 000 ₽</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеонаблюдению и услуги по обеспечению видеосъемки и видеозаписи проведения единого государственного экзамена в 2026 году</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/92979830-tender-okazanie-uslug-po-videonablyudeniyu-i-uslugi-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-edinogo-gosudarstvennogo-ekzamena-v</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2 801 638 ₽</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по видеосъемке спектакля шурале. история одной семьи в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92979549-tender-okazanie-uslugi-po-videosemke-spektaklya-shurale-istoriya-odnoj-semi</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>41 100 ₽</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации поверки дорожной лаборатории кп-514 rdt в Барнауле</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/barnaul/92948589-tender-okazanie-uslug-po-organizacii-poverki-dorojnoj-laboratorii-kp-514-rdt</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>399 183 ₽</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Тендер на закупку фотоаппаратов в Новокуйбышевске</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>/region/samarskaya-oblast/novokujbyshevsk/92972589-tender-zakupka-fotoapparatov</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по обеспечению видеосъемки фестиваля исторической реконструкции в Великом Новгороде</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>/region/novgorodskaya-oblast/velikij-novgorod/92970238-tender-okazanie-kompleksa-uslug-po-obespecheniyu-videosemki-festivalya-istoricheskoj-rekonstrukcii</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>450 000 ₽</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Тендер бытовая техника. обслуживание. ремонт. фото- и видео товары.. съемка и монтаж видеоролика (видеопрезентация) для участия в федеральном конкурсе лучшая детская школа искусств в Уфе</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/92969755-tender-bytovaya-tehnika-obslujivanie-remont-foto-i-video-tovary-semka-i-montaj-videorolika-videoprezentaciya-dlya-uchastiya-v</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>35 000 ₽</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъёмки обучающей, культурно-деловой и экскурсионной программ форума северо-западного федерального округа, посвященного 10-летию движения юнармия в Вологде</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>/region/vologodskaya-oblast/vologda/92968778-tender-okazanie-uslug-po-organizacii-videosemki-obuchayushchej-kulturno-delovoj-i-ekskursionnoj-programm-foruma-severo-zapadnogo</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>40 000 ₽</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению фото- и видеосъемки на территории проведения мероприятий и обработке материалов для нужд санкт-петербургского филиала ано дпо техническая академия росатома в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92957061-tender-okazanie-uslug-po-provedeniyu-foto-i-videosemki-na-territorii-provedeniya-meropriyatij-i-obrabotke-materialov-dlya-nujd-sankt</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению регионального проекта юный глава в Челябинске</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>/region/chelyabinskaya-oblast/chelyabinsk/92950687-tender-okazanie-uslug-po-organizacii-i-provedeniyu-regionalnogo-proekta-yunyj-glava</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2 398 999 ₽</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Тендер , оказание комплекса услуг по сопровождению всероссийского конкурса камера.поход.россия в Орле</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>/region/orlovskaya-oblast/orel/92928458-tender-okazanie-kompleksa-uslug-po-soprovojdeniyu-vserossijskogo-konkursa-kamerapohodrossiya</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>9 507 776 ₽</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению iv слета лидеров молодежных советов компаний в Москве</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92919948-tender-okazanie-uslug-po-organizacii-i-provedeniyu-iv-sleta-liderov-molodejnyh-sovetov-kompanij</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2 498 663 ₽</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по профессиональной видеосъемке открытого урока по учебному предмету "станковая композиция" для участия во ii окружном этапе общероссийского конкурса "лучший преподаватель детской школы искусств" в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92908725-tender-uslugi-po-professionalnoj-videosemke-otkrytogo-uroka-po-uchebnomu-predmetu-stankovaya-kompoziciya-dlya-uchastiya-vo-ii-okrujnom</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>17 500 ₽</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>06.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по созданию мультимедийных материалов в рамках проекта иммерсивная прогулка живые страницы центрального района в спб гбук мцбс им. м.ю. лермонтова в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92900754-tender-okazanie-uslug-po-sozdaniyu-multimedijnyh-materialov-v-ramkah-proekta-immersivnaya-progulka-jivye-stranicy-centralnogo-rajona-v-spb</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>150 000 ₽</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>06.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению фото- и видеосъемки и обработки материалов для ано дпо техническая академия росатома и сторонних организаций в Обнинске</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>/region/kalujskaya-oblast/obninsk/92897480-tender-okazanie-uslug-po-provedeniyu-foto-i-videosemki-i-obrabotki-materialov-dlya-ano-dpo-tehnicheskaya-akademiya-rosatoma-i-storonnih</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению военно-полевых сборов</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/92874878-tender-okazanie-uslug-po-organizacii-i-provedeniyu-voenno-polevyh-sborov</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>21 846 000 ₽</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по видеосъемке, фотосъемке и монтажу видеороликов ii всероссийского форума молодых студенческих семей в Вологде</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>/region/vologodskaya-oblast/vologda/92881320-tender-uslugi-po-videosemke-fotosemke-i-montaju-videorolikov-ii-vserossijskogo-foruma-molodyh-studencheskih-semej</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>270 500 ₽</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации видеосъёмки в рамках фестиваля молодого кино новое движение в Великом Новгороде</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>/region/novgorodskaya-oblast/velikij-novgorod/92873392-tender-uslugi-po-organizacii-videosemki-v-ramkah-festivalya-molodogo-kino-novoe-dvijenie</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>1 159 164 ₽</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>04.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации мероприятия, фото и видеосъемки мероприятия в Тихвине</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/tihvin/92874090-tender-uslugi-po-organizacii-meropriyatiya-foto-i-videosemki-meropriyatiya</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>40 300 ₽</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеотрансляции на светодиодные экраны хоровой акции многоголосая тюмень – тебе россия! в Тюмени</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/tyumen/92855257-tender-okazanie-uslug-po-organizacii-videotranslyacii-na-svetodiodnye-ekrany-horovoj-akcii-mnogogolosaya-tyumen-tebe-rossiya</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>606 900 ₽</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому обеспечению мероприятия (региональные финалы) по развитию молодежного предпринимательства "я в деле" (в части обеспечения питания, питьевого режима, фото и видеосъемки, канцелярской и типографской продукцией), направленного на повышение компетенции наставников в 2026 году в Иркутске</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>/tender/92848107</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке, монтажу и изготовлению видеоролика об экологическом проекте жизнь камчатскому лососю! в Петропавловске-Камчатском</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>/region/kamchatskij-kraj/petropavlovsk-kamchatskij/92837898-tender-okazanie-uslug-po-videosemke-montaju-i-izgotovleniyu-videorolika-ob-ekologicheskom-proekte-jizn-kamchatskomu</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и созданию пилотного виртуального ролика</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>/region/irkutskaya-oblast/92837446-tender-okazanie-uslug-po-videosemke-i-sozdaniyu-pilotnogo-virtualnogo-rolika</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому обеспечению проведения четвертого фестиваля стран латинской америки в санкт-петербурге в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92830588-tender-okazanie-uslug-po-organizacionno-tehnicheskomu-obespecheniyu-provedeniya-chetvertogo-festivalya-stran-latinskoj-ameriki-v-sankt</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>4 486 160 ₽</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Тендер на оказание информационных услуг по подготовке, размещению материалов (телепередач, репортажей, роликов), освещающих вопросы деятельности органов мо северский муниципальный район краснодарского края на 2026 год для администрации муниципального образования северский муниципальный район краснодарского края</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/92827117-tender-okazanie-informacionnyh-uslug-po-podgotovke-razmeshcheniyu-materialov-teleperedach-reportajej-rolikov-osveshchayushchih-voprosy</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>800 000 ₽</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг в рамках подготовки слушателей дополнительных профессиональных программ повышения квалификации в Ярославле</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>/region/yaroslavskaya-oblast/yaroslavl/92827040-tender-okazanie-kompleksa-uslug-v-ramkah-podgotovki-slushatelej-dopolnitelnyh-professionalnyh-programm-povysheniya-kvalifikacii</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>17 509 560 ₽</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеотрансляции мероприятия многоголосая тюмень в Тюмени</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/tyumen/92809857-tender-okazanie-uslug-po-organizacii-videotranslyacii-meropriyatiya-mnogogolosaya-tyumen</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>606 900 ₽</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>04.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото и видеосъемке в Краснодаре</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/krasnodar/92810444-tender-okazanie-uslug-po-foto-i-videosemke</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>195 000 ₽</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по организации и проведению торжественного вручения дипломов выпускникам в Люберцах</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/lyubercy/92788948-tender-okazanie-uslugi-po-organizacii-i-provedeniyu-torjestvennogo-vrucheniya-diplomov-vypusknikam</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеонаблюдению и услуги по обеспечению видеосъемки и видеозаписи проведения единого государственного экзамена в 2026 году в Раменском</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/ramenskoe/92784922-tender-okazanie-uslug-po-videonablyudeniyu-i-uslugi-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-edinogo-gosudarstvennogo</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>03.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Тендер на разработку фотостилистики бренда siberian express</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/92753287-tender-razrabotka-fotostilistiki-brenda-siberian-express</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению похода, приуроченного ко дню народных ремесел и промыслов в рамках серии походов время открытий в Якутске</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>/region/saha-yakutiya-respublika/yakutsk/92765624-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-pohoda-priurochennogo-ko-dnyu-narodnyh-remesel-i-promyslov-v-ramkah</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3 542 663 ₽</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по фото и видеосъёмке мероприятий в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92760808-tender-okazanie-uslugi-po-foto-i-videosemke-meropriyatij</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>220 000 ₽</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>02.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению мероприятия молодёжный фестиваль?26 в 2026 году в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92753525-tender-okazanie-uslug-po-organizacii-i-provedeniyu-meropriyatiya-molodejnyj-festival26-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>450 000 ₽</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке с последующей трансляцией в социальные сети арт-кластера таврида в Судаке</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>/region/krym-respublika/sudak/92728551-tender-okazanie-uslug-po-videosemke-s-posleduyushchej-translyaciej-v-socialnye-seti-art-klastera-tavrida</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>8 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по фото и видео сопровождению мероприятия, обеспечению видеосъемки и изготовлению видеороликов, аренде студии записи, обеспечению трансляции, техническому сопровождению всероссийского форума "шерегеш в Кемерово</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>/region/kemerovskaya-oblast/kemerovo/92731898-tender-uslugi-po-foto-i-video-soprovojdeniyu-meropriyatiya-obespecheniyu-videosemki-i-izgotovleniyu-videorolikov-arende-studii</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>1 120 000 ₽</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации фото- и видеосопровождения в рамках программы развития доступности поддержки молодежных инициатив в сельских территориях проектный десант в Кемерово</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>/region/kemerovskaya-oblast/kemerovo/92731848-tender-uslugi-po-organizacii-foto-i-videosoprovojdeniya-v-ramkah-programmy-razvitiya-dostupnosti-podderjki-molodejnyh-iniciativ-v</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации фото- видеосопровождения в рамках программы кузбасс молодых. муниципалитеты в Кемерово</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>/region/kemerovskaya-oblast/kemerovo/92731759-tender-uslugi-po-organizacii-foto-videosoprovojdeniya-v-ramkah-programmy-kuzbass-molodyh-municipalitety</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по обеспечению видеосъемки и видеозаписи проведения государственной итоговой аттестации и единого государственного экзамена</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>/region/komi-respublika/92717044-tender-uslugi-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-gosudarstvennoj-itogovoj-attestacii-i-edinogo-gosudarstvennogo-ekzamena</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>14 548 270 ₽</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Тендер на оказание организационных услуг , а именно услуг по организации, проведению и сопровождению: конференций, круглых столов, мастер-классов, совещаний, семинаров, вебинаров, стратегических сессий в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>/tender/92729598</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>80 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Тендер видеосъемка, изготовление корпоративного видеоролика в Тюмени</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/tyumen/92716959-tender-videosemka-izgotovlenie-korporativnogo-videorolika</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по предоставлению сервисов верхового визуального осмотра с применением фото и видеосъемки</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/92711118-tender-okazanie-uslug-po-predostavleniyu-servisov-verhovogo-vizualnogo-osmotra-s-primeneniem-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>9 440 551 ₽</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Тендер на проведение видеосъемки мероприятия в Перми</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/perm/92704160-tender-provedenie-videosemki-meropriyatiya</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>50 500 ₽</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>29.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по изготовлению и размещению рекламных материалов (радио, экраны, рся) в Пензе</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>/region/penzenskaya-oblast/penza/92691340-tender-uslugi-po-izgotovleniyu-i-razmeshcheniyu-reklamnyh-materialov-radio-ekrany-rsya</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>1 266 631 ₽</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>04.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение фото и видеосъемки ооо максима групп (сеть универмагов familia)</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92686337-tender-organizaciya-i-provedenie-foto-i-videosemki-ooo-maksima-grupp-set-univermagov-familia</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>31.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото и видеосъёмке мероприятий</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92675541-tender-okazanie-uslug-po-foto-i-videosemke-meropriyatij</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению студенческой конференции в области развития избирательного права и избирательного процесса, повышения правовой и политической культуры избирателей и организаторов выборов в Казани</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/kazan/92689623-tender-okazanie-uslug-po-organizacii-i-provedeniyu-studencheskoj-konferencii-v-oblasti-razvitiya-izbiratelnogo-prava-i-izbiratelnogo</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>388 846 ₽</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по фото, видеосъемке помещения и созданию презентационного ролика объекта строительства в Москве</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92687325-tender-uslugi-po-foto-videosemke-pomeshcheniya-i-sozdaniyu-prezentacionnogo-rolika-obekta-stroitelstva</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по проведению многокамерной видеосъемки мероприятия "детский фестиваль "игровая фабрика профессий" бегуницкого дома культуры и по проведению мастер-класса по репортажной съемке 30.05.2026, 14:00-16:00</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/92683820-tender-uslugi-po-provedeniyu-mnogokamernoj-videosemki-meropriyatiya-detskij-festival-igrovaya-fabrika-professij-begunickogo-doma-kultury-i</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>15 000 ₽</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>29.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению досуговых мероприятий "семья" и "живой звук!" для жителей внутригородского муниципального образования города федерального значения санкт-петербурга поселок шушары</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92654224-tender-okazanie-uslug-po-organizacii-i-provedeniyu-dosugovyh-meropriyatij-semya-i-jivoj-zvuk-dlya-jitelej-vnutrigorodskogo-municipalnogo</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>174 700 ₽</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению регионального форума родные-любимые в Челябинске</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>/region/chelyabinskaya-oblast/chelyabinsk/92644977-tender-okazanie-uslug-po-organizacii-i-provedeniyu-regionalnogo-foruma-rodnye-lyubimye</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>848 999 ₽</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>03.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по видеосъемке мероприятия концерт макс-шоу балет в Березниках</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/berezniki/92633149-tender-uslugi-po-videosemke-meropriyatiya-koncert-maks-shou-balet</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>20 000 ₽</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Тендер штатив для фотоаппарата, телефона, видеокамеры микрофон петличный свет портативный для фото- и видеосъемки в Саратове</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>/region/saratovskaya-oblast/saratov/92631150-tender-shtativ-dlya-fotoapparata-telefona-videokamery-mikrofon-petlichnyj-svet-portativnyj-dlya-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>9 726 ₽</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Тендер на оказание по проведению походного мероприятия в рамках серии походов "время открытий" (проект "походы первых – больше, чем путешествие") на базе резиденции арт-кластера "таврида" "счастливцево" в Херсоне</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>/region/khersonskaya-oblast/kherson/92610128-tender-okazanie-po-provedeniyu-pohodnogo-meropriyatiya-v-ramkah-serii-pohodov-vremya-otkrytij-proekt-pohody-pervyh-bolshe-chem</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2 218 009 ₽</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>03.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению техникой и стендов наглядной агитации для нужд фку ик-5 уфсин россии по рязанской области</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>/region/ryazanskaya-oblast/92607798-tender-okazanie-uslug-po-obespecheniyu-tehnikoj-i-stendov-naglyadnoj-agitacii-dlya-nujd-fku-ik-5-ufsin-rossii-po-ryazanskoj-oblasti</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>316 000 ₽</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>29.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг на многокамерную профессиональную видеосъемку спектакля с монтажом в Сургуте</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/surgut/92605409-tender-okazanie-uslug-na-mnogokamernuyu-professionalnuyu-videosemku-spektaklya-s-montajom</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>28.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Тендер на услуги в области фото и видеосъемки в Арске</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/arsk/92595560-tender-uslugi-v-oblasti-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>80 000 ₽</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>28.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки и видеозаписи проведения основного, дополнительного периода единого государственного экзамена на территории чеченской республики в 2026 году в Грозном</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>/region/chechenskaya-respublika/groznyj/92555579-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-osnovnogo-dopolnitelnogo-perioda-edinogo</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>7 935 413 ₽</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>02.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского форума пространство воспитания: диалог, традиции, единство</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>/tender/92577821</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>25 987 336 ₽</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Тендер услуга по фото и видеосъемке мероприятия (семейный пикник) в Калуге</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>/region/kalujskaya-oblast/kaluga/92571701-tender-usluga-po-foto-i-videosemke-meropriyatiya-semejnyj-piknik</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Тендер производство видеоконтента в промышленной зоне исправительного учреждения в Южно-Сахалинске</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>/region/sahalinskaya-oblast/yujno-sahalinsk/92549165-tender-proizvodstvo-videokontenta-v-promyshlennoj-zone-ispravitelnogo-uchrejdeniya</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>15 000 ₽</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Тендер оказать услуг по изготовлению видеоролика социальной рекламы в Омске</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>/region/omskaya-oblast/omsk/92544789-tender-okazat-uslug-po-izgotovleniyu-videorolika-socialnoj-reklamy</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>150 000 ₽</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению культурно-массовых мероприятий для хабаровского дворца культуры железнодорожников в Хабаровске</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>/region/habarovskij-kraj/habarovsk/92544602-tender-okazanie-uslug-po-provedeniyu-kulturno-massovyh-meropriyatij-dlya-habarovskogo-dvorca-kultury-jeleznodorojnikov</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>462 488 ₽</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки и видеозаписи проведения единого государственного экзамена в 2026 году (00006332-эа) в Чите</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>/region/zabajkalskij-kraj/chita/92542835-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-edinogo-gosudarstvennogo-ekzamena-v-2026-godu-00006332-ea</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>20 928 000 ₽</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>03.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Тендер на услуги организации фотосессий, монтаж (фото и видео съемки), направленных на популяризацию продуктов заказчика в Москве</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92518677-tender-uslugi-organizacii-fotosessij-montaj-foto-i-video-semki-napravlennyh-na-populyarizaciyu-produktov-zakazchika</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъемки и обеспечению прямой трансляции в информационно-телекоммуникационную сеть интернет iii кузбасский форум креативных индустрий в Кемерово</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>/region/kemerovskaya-oblast/kemerovo/92512403-tender-okazanie-uslug-po-organizacii-videosemki-i-obespecheniyu-pryamoj-translyacii-v-informacionno-telekommunikacionnuyu-set</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>40 715 ₽</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Тендер услуга по техническому и программному обеспечению видеосъемки проведения специализированного клинического интервью по стандартизированной операционной процедуре проведения этологического исследования с использованием биометрической видеорегистрации</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92499844-tender-usluga-po-tehnicheskomu-i-programmnomu-obespecheniyu-videosemki-provedeniya-specializirovannogo-klinicheskogo-intervyu-po</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по диагностике состояния участков автомобильных дорог и по разработке проектов организации дорожного движения автомобильных дорог общего пользования регионального значения архангельской области в Архангельске</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>/region/arhangelskaya-oblast/arhangelsk/92492650-tender-vypolnenie-rabot-po-diagnostike-sostoyaniya-uchastkov-avtomobilnyh-dorog-i-po-razrabotke-proektov-organizacii-dorojnogo</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>14 959 633 ₽</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>29.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъемки в студии исполнителя в Москве</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92477444-tender-okazanie-uslug-po-organizacii-videosemki-v-studii-ispolnitelya</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъемки в студии исполнителя в Москве</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92477614-tender-okazanie-uslug-po-organizacii-videosemki-v-studii-ispolnitelya</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Тендер фото на паспорт в Микуне</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>/region/komi-respublika/mikun/92475536-tender-foto-na-pasport</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>600 ₽</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по предоставлению презентационных материалов (видеосъемка) в Иркутске</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>/region/irkutskaya-oblast/irkutsk/92449757-tender-uslugi-po-predostavleniyu-prezentacionnyh-materialov-videosemka</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>21.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации и проведению многокамерной видеосъемки в режиме прямого эфира пленарной сессии в рамках чебоксарского экономического форума, включая создание итогового видеоролика хронометражем до 3 мин. 2026г</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>/region/chuvashskaya---chuvashiya-respublika/92447838-tender-uslugi-po-organizacii-i-provedeniyu-mnogokamernoj-videosemki-v-rejime-pryamogo-efira-plenarnoj-sessii-v-ramkah</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2 746 700 ₽</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по дихайну полиграфической продукции, изготовлению видео-контента, видеосъемке и созданию итогового ролика, а также размещению информации в виде спецпроекта на сайте drugoigorod.ru при организации и проведении общегородского мероприятия, посвященного всероссийской акции «ночь музеев</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>/tender/30590070999</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>560 850 ₽</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>20.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Тендер оказать услуг по изготовлению видеоролика социальной рекламы в Омске</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>/region/omskaya-oblast/omsk/92434047-tender-okazat-uslug-po-izgotovleniyu-videorolika-socialnoj-reklamy</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>150 000 ₽</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>21.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по видеосъемке мероприятия концерт школы-студии апельсин в Березниках</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/berezniki/92431804-tender-uslugi-po-videosemke-meropriyatiya-koncert-shkoly-studii-apelsin</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>20 000 ₽</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>20.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке с последующей трансляцией в социальные сети арт-кластера таврида в Судаке</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>/region/krym-respublika/sudak/92427533-tender-okazanie-uslug-po-videosemke-s-posleduyushchej-translyaciej-v-socialnye-seti-art-klastera-tavrida</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации выделенного виртуального канала связи между объектами, указанными в приложении №2 и цод исполнителя, в целях передачи видеоданных с видеосъемкой проведения единого государственного экзамена на территории курской области в 2026г</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>/tender/30590073698</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>363 948 ₽</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>19.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг в рамках проекта по нейропрофилированию детей и молодежи в Москве</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>/tender/92426707</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>11 090 000 ₽</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>04.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению общественно-значимых и официальных мероприятий, организуемых правительством ярославской области во втором полугодии 2026 года в Ярославле</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>/region/yaroslavskaya-oblast/yaroslavl/92421506-tender-okazanie-uslug-po-organizacii-i-provedeniyu-obshchestvenno-znachimyh-i-oficialnyh-meropriyatij-organizuemyh-pravitelstvom</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>1 649 109 ₽</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению полуфинала всероссийского конкурса наставников быть, а не казаться для южного и северо-кавказского федеральных округов</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>/region/volgogradskaya-oblast/92386887-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-polufinala-vserossijskogo-konkursa-nastavnikov-byt-a-ne-kazatsya-dlya-yujnogo</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>20 240 000 ₽</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>03.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению финала международного фестиваля-конкурса патриотической песни солдатский конверт - 2026 в Москве</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92385897-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-finala-mejdunarodnogo-festivalya-konkursa-patrioticheskoj-pesni-soldatskij-konvert-2026</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>8 414 000 ₽</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению конференции, посвященной изучению городской скульптуры в 2026 году в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92366170-tender-okazanie-uslug-po-organizacii-i-provedeniyu-konferencii-posvyashchennoj-izucheniyu-gorodskoj-skulptury-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>500 000 ₽</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>19.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки и видеозаписи проведения единого государственного экзамена в 2026 году в пунктах проведения экзаменов</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>/region/amurskaya-oblast/92364020-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-edinogo-gosudarstvennogo-ekzamena-v-2026-godu-v-punktah-provedeniya</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>13 937 546 ₽</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>21.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Тендер ptz-камера для комплекса видеоконференцсвязи в Абакане</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>/region/hakasiya-respublika/abakan/92359789-tender-ptz-kamera-dlya-kompleksa-videokonferencsvyazi</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>28.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Тендер на оказание по проведению походного мероприятия в рамках серии походов "время открытий" (проект "походы первых – больше, чем путешествие") на базе резиденции арт-кластера "таврида" "счастливцево"</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>/region/khersonskaya-oblast/92346433-tender-okazanie-po-provedeniyu-pohodnogo-meropriyatiya-v-ramkah-serii-pohodov-vremya-otkrytij-proekt-pohody-pervyh-bolshe-chem-puteshestvie</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по созданию видеоконтента, в рамках организации и проведения праздничного концерта, посвященного дню россии в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/92333052-tender-okazanie-uslug-po-sozdaniyu-videokontenta-v-ramkah-organizacii-i-provedeniya</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>295 000 ₽</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки и видеозаписи проведения государственной итоговой аттестации в 2026 году в Мурманске</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>/region/murmanskaya-oblast/murmansk/92348662-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-gosudarstvennoj-itogovoj-attestacii-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>1 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>20.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки и видеозаписи проведения государственной итоговой аттестации в 2026 году в Мурманске</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>/region/murmanskaya-oblast/murmansk/92348582-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-gosudarstvennoj-itogovoj-attestacii-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>1 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>20.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению мероприятия церемония открытия российской галереи искусств в Севастополе</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>/region/sevastopol-gorod/92347142-tender-okazanie-uslug-po-organizacii-i-provedeniyu-meropriyatiya-ceremoniya-otkrytiya-rossijskoj-galerei-iskusstv</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>70 900 000 ₽</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки и видеозаписи проведения единого государственного экзамена в 2026 году в Абазе</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>/region/hakasiya-respublika/abaza/92316645-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-edinogo-gosudarstvennogo-ekzamena-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>8 054 712 ₽</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по профессиональной видеосъемке, монтажу видеоматериала, созданию фильма конкурсной программы малых форм в рамках xxvii международного фестиваля «славянские театральные встречи</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>/tender/30590065497</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>117 000 ₽</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Тендер на приобретение оборудования для фото и видеосъемки в Бабаево</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>/region/vologodskaya-oblast/babaevo/92330656-tender-priobretenie-oborudovaniya-dlya-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>1 922 634 ₽</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Тендер на приобретение оборудования для фото и видеосъемки в Бабаево</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>/region/vologodskaya-oblast/babaevo/92330501-tender-priobretenie-oborudovaniya-dlya-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>1 002 785 ₽</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки, видеозаписи при проведении единого государственного экзамена в 2026 году на территории республики ингушетия</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>/region/ingushetiya-respublika/92311464-tender-okazanie-uslug-po-obespecheniyu-videosemki-videozapisi-pri-provedenii-edinogo-gosudarstvennogo-ekzamena-v-2026-godu-na-territorii</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>14 209 170 ₽</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Тендер buy-77809 выбор пула продакшенов на 2 года (услуги видеосъемки)</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92312309-tender-buy-77809-vybor-pula-prodakshenov-na-2-goda-uslugi-videosemki</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>28.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение фото-видеосъемки конкурса "лучший по профессии" 2026 года в Новороссийске</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/novorossijsk/92321482-tender-organizaciya-i-provedenie-foto-videosemki-konkursa-luchshij-po-professii-2026-goda</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>260 000 ₽</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>28.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению похода, приуроченного ко всемирному дню окружающей среды (дню эколога) в рамках серии походов время открытий в Мурманске</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>/region/murmanskaya-oblast/murmansk/92295364-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-pohoda-priurochennogo-ko-vsemirnomu-dnyu-okrujayushchej-sredy-dnyu</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>3 310 887 ₽</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки и видеозаписи проведения государственной итоговой аттестации в 2026 году в Мурманске</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>/region/murmanskaya-oblast/murmansk/92312607-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-gosudarstvennoj-itogovoj-attestacii-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>24 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Тендер ми №64/ми (26р009) - услуги по фото- и видеосъемке для нужд ооо газпром энергохолдинг индустриальные активы в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>/tender/92311158</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>600 000 ₽</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организационному сопровождению (техническому обеспечению) видеосъемки заказчиком социального мероприятия "концерт солистов цмш-академии исполнительского искусства" в большом зале гбук г. москвы "мкз "зарядье в Москве</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92293232-tender-uslugi-po-organizacionnomu-soprovojdeniyu-tehnicheskomu-obespecheniyu-videosemki-zakazchikom-socialnogo-meropriyatiya-koncert-solistov-cmsh</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>120 000 ₽</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>19.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото-и видеосъемке и изготовлению видеоконтента для нужд филиала пао россети центр и приволжье – удмуртэнерго</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>/region/udmurtskaya-respublika/92247684-tender-okazanie-uslug-po-foto-i-videosemke-i-izgotovleniyu-videokontenta-dlya-nujd-filiala-pao-rosseti-centr-i-privolje-udmurtenergo</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>349 999 ₽</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>19.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъёмке, фотосъёмке и изготовлению видеоролика мероприятия в рамках регионального этапа всероссийского конкурса профессионального мастерства лучший по профессии в Богородицке</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>/region/tulskaya-oblast/bogorodick/92274590-tender-okazanie-uslug-po-videosemke-fotosemke-i-izgotovleniyu-videorolika-meropriyatiya-v-ramkah-regionalnogo-etapa-vserossijskogo</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>45 700 ₽</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъёмке, фотосъёмке и изготовлению видеоролика мероприятия в рамках регионального этапа всероссийского конкурса профессионального мастерства лучший по профессии в Богородицке</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>/region/tulskaya-oblast/bogorodick/92274129-tender-okazanie-uslug-po-videosemke-fotosemke-i-izgotovleniyu-videorolika-meropriyatiya-v-ramkah-regionalnogo-etapa-vserossijskogo</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>45 700 ₽</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационному и методическому обеспечению проведения мероприятий международного проекта vi петербургская международная неделя балалайки русское чудо в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92272355-tender-okazanie-uslug-po-organizacionnomu-i-metodicheskomu-obespecheniyu-provedeniya-meropriyatij-mejdunarodnogo-proekta-vi-peterburgskaya</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>11 462 100 ₽</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>29.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведения регионального этапа международной конкурс-премии кардо в Салехарде</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>/region/yamalo-neneckij-avtonomnyj-okrug/salehard/92258731-tender-okazanie-uslug-po-organizacii-i-provedeniya-regionalnogo-etapa-mejdunarodnoj-konkurs-premii-kardo</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>540 900 ₽</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки и видеозаписи проведения государственной итоговой аттестации в 2026 году в Мурманске</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>/region/murmanskaya-oblast/murmansk/92238774-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-gosudarstvennoj-itogovoj-attestacii-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>24 500 000 ₽</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>28.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по профессиональной фотосъёмке работников, пост-обработке фотографий и каталогизированию результатов для нужд гуп петербургский метрополитен в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>/tender/92235719</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению видеосъемки для нужд пао россети северо-запад, с учетом оказания сопутствующих услуг монтаж, обработка, цветокоррекция в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92222622-tender-okazanie-uslug-po-provedeniyu-videosemki-dlya-nujd-pao-rosseti-severo-zapad-s-uchetom-okazaniya-soputstvuyushchih-uslug-montaj</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>477 752 ₽</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>19.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому обеспечению проведения межрегионального мероприятия дни санкт-петербурга в вологодской области в Вологде</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>/region/vologodskaya-oblast/vologda/92202193-tender-okazanie-uslug-po-organizacionno-tehnicheskomu-obespecheniyu-provedeniya-mejregionalnogo-meropriyatiya-dni-sankt-peterburga-v</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>7 317 806 ₽</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>25.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг и выполнение работ по организации и проведению общеразвивающей, атмосферной, практической программ, обеспечению фотосъемки и видеосъемки международного фестиваля детства и юности "фестиваль движения первых" (ид 26_45424) в Москве</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92201579-tender-okazanie-uslug-i-vypolnenie-rabot-po-organizacii-i-provedeniyu-obshcherazvivayushchej-atmosfernoj-prakticheskoj-programm-obespecheniyu</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>59 999 999 ₽</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению спортивного мероприятия спортивный ярославль в Ярославле</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>/region/yaroslavskaya-oblast/yaroslavl/92201250-tender-okazanie-uslug-po-organizacii-i-provedeniyu-sportivnogo-meropriyatiya-sportivnyj-yaroslavl</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>1 738 306 ₽</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>19.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по монтажу и техническому обслуживанию оборудования сценического комплекса, его художественному оформлению, а также оснащению средствами видеосъёмки и трансляции для мероприятия в Балашихе</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/balashiha/92198945-tender-okazanie-kompleksa-uslug-po-montaju-i-tehnicheskomu-obslujivaniyu-oborudovaniya-scenicheskogo-kompleksa-ego-hudojestvennomu</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>7 220 000 ₽</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского форума президентов школ в Москве</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92199716-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-foruma-prezidentov-shkol</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>20 905 401 ₽</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>25.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации приемов иностранных делегаций в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92188723-tender-okazanie-uslug-po-organizacii-priemov-inostrannyh-delegacij</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>39 500 500 ₽</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации выделенного виртуального канала связи между объектами, в целях передачи видеоданных с видеосъемкой в Раменском</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/ramenskoe/92186297-tender-okazanie-uslug-po-organizacii-vydelennogo-virtualnogo-kanala-svyazi-mejdu-obektami-v-celyah-peredachi-videodannyh-s</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>266 322 ₽</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>20.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке с последующей трансляцией в социальные сети арт-кластера таврида в Судаке</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>/region/krym-respublika/sudak/92169242-tender-okazanie-uslug-po-videosemke-s-posleduyushchej-translyaciej-v-socialnye-seti-art-klastera-tavrida</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Тендер услуга по фотографированию руководителя министерства. фотографии будут использованы для полиграфической продукции в подведомственных учреждениях, а также для иллюстрации открыток, поздравительных телеграмм и публикаций в официальных информационных источниках в Иркутске</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>/region/irkutskaya-oblast/irkutsk/92170893-tender-usluga-po-fotografirovaniyu-rukovoditelya-ministerstva-fotografii-budut-ispolzovany-dlya-poligraficheskoj-produkcii-v</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>12.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению фото- и видеосъемки фестиваля-форума российская креативная неделя в 2026 году в Москве</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92169549-tender-okazanie-uslug-po-organizacii-i-provedeniyu-foto-i-videosemki-festivalya-foruma-rossijskaya-kreativnaya-nedelya-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>1 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Тендер товары информационно-технологические, средства связи, оргтехника, электроника (включая программное обеспечение) в Москве</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92165946-tender-tovary-informacionno-tehnologicheskie-sredstva-svyazi-orgtehnika-elektronika-vklyuchaya-programmnoe-obespechenie</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>220 013 ₽</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг в области фото- и видеосъемки событий в Луганске</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>/region/luganskaya-narodnaya-respublika/lugansk/92162360-tender-okazanie-uslug-v-oblasti-foto-i-videosemki-sobytij</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке театральных постановок театра драмы кузбасса (премьер спектаклей) на несколько камер в течение 2026 года с последующим монтажом в Кемерово</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>/region/kemerovskaya-oblast/kemerovo/92149461-tender-okazanie-uslug-po-videosemke-teatralnyh-postanovok-teatra-dramy-kuzbassa-premer-spektaklej-na-neskolko-kamer-v-techenie-2026</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>90 425 ₽</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъемки и прямой онлайн-видеотрансляции проведения конференции гиа-2026 в Махачкале</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>/region/dagestan-respublika/mahachkala/92143177-tender-okazanie-uslug-po-organizacii-videosemki-i-pryamoj-onlajn-videotranslyacii-provedeniya-konferencii-gia-2026</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>67 600 ₽</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Тендер на закупку в области: услуги в области фото- и видеосъемки событий в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92134812-tender-zakupka-v-oblasti-uslugi-v-oblasti-foto-i-videosemki-sobytij</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>587 796 ₽</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг и выполнение работ по организации и проведению общеразвивающей, атмосферной, практической программ, обеспечению фотосъемки и видеосъемки международного фестиваля детства и юности "фестиваль движения первых" (ид 26/45424) в Москве</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92133001-tender-okazanie-uslug-i-vypolnenie-rabot-po-organizacii-i-provedeniyu-obshcherazvivayushchej-atmosfernoj-prakticheskoj-programm-obespecheniyu</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению всероссийского исследовательского конкурса семейная память в Москве</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92128175-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-vserossijskogo-issledovatelskogo-konkursa-semejnaya-pamyat</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>5 976 000 ₽</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению полуфинала всероссийского конкурса наставников быть, а не казаться для дальневосточного федерального округа в Владивостоке</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>/region/primorskij-kraj/vladivostok/92128185-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-polufinala-vserossijskogo-konkursa-nastavnikov-byt-a-ne-kazatsya-dlya</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>8 968 000 ₽</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению профессиональной фото/видеосъёмки брендированной продукции в Москве</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92115304-tender-okazanie-uslug-po-provedeniyu-professionalnoj-fotovideosemki-brendirovannoj-produkcii</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>9 190 400 ₽</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>16.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по чистке корпуса судна, замерам остаточных толщин, замерам зазоров и проведения подводной видеосъемки катера «лк-12</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>/tender/30590059663</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>595 000 ₽</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>06.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение церемонии чествования лучших выпускников профессиональных образовательных организаций санкт-петербурга в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92115639-tender-organizaciya-i-provedenie-ceremonii-chestvovaniya-luchshih-vypusknikov-professionalnyh-obrazovatelnyh-organizacij-sankt-peterburga</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>661 048 ₽</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Тендер услуг изготовления визуального контента и администрирования социальных сетей при проведении официальной лиги запсиб тюменской области международного союза квн в Тюмени</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/tyumen/92087087-tender-uslug-izgotovleniya-vizualnogo-kontenta-i-administrirovaniya-socialnyh-setej-pri-provedenii-oficialnoj-ligi-zapsib-tyumenskoj</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>180 000 ₽</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъемки в рамках проведения спортивных соревнований в Балаково</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>/region/saratovskaya-oblast/balakovo/92099310-tender-okazanie-uslug-po-organizacii-videosemki-v-ramkah-provedeniya-sportivnyh-sorevnovanij</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>860 000 ₽</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>06.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению мероприятий открытого конкурса в Москве</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92099023-tender-okazanie-uslug-po-organizacii-i-provedeniyu-meropriyatij-otkrytogo-konkursa</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>8 673 569 ₽</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому обеспечению проведения научно-практической конференции с международным участием "инвазивные виды как потенциальная угроза биологической безопасности россии: вызовы и риски" в части обеспечения оснащения системы регистрации, синхронного перевода, видеосъемки, изготовления полиграфической и широкоформатной продукции, выполнения работ по монтажу/демонтажу и оклейке поверхностей и оформления зала</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/92098067-tender-okazanie-uslug-po-organizacionno-tehnicheskomu-obespecheniyu-provedeniya-nauchno-prakticheskoj-konferencii-s-mejdunarodnym-uchastiem</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>06.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и монтажу короткометражного документального фильма, посвященному году единства народов россии, в рамках праздничной программы, посвященной дню народного единства в Тюмени</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/tyumen/92089011-tender-okazanie-uslug-po-videosemke-i-montaju-korotkometrajnogo-dokumentalnogo-filma-posvyashchennomu-godu-edinstva-narodov-rossii-v</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>500 000 ₽</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>07.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению серии мероприятий, направленных на развитие добровольчества (волонтерства)</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/92086868-tender-okazanie-uslug-po-organizacii-i-provedeniyu-serii-meropriyatij-napravlennyh-na-razvitie-dobrovolchestva-volonterstva</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>33 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению уличного фестиваля мыпетербург в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92084730-tender-okazanie-uslug-po-organizacii-i-provedeniyu-ulichnogo-festivalya-mypeterburg</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>698 450 ₽</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению полуфинала всероссийского конкурса наставников быть, а не казаться для уральского и приволжского федеральных округов в Каменске-Уральском</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>/region/sverdlovskaya-oblast/kamensk-uralskij/92076403-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-polufinala-vserossijskogo-konkursa-nastavnikov-byt-a-ne</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>21 148 000 ₽</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Тендер товары информационно-технологические, средства связи, оргтехника, электроника (включая программное обеспечение) в Москве</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92081930-tender-tovary-informacionno-tehnologicheskie-sredstva-svyazi-orgtehnika-elektronika-vklyuchaya-programmnoe-obespechenie</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>363 351 ₽</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>06.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по обследованию и видеосъёмке верхнего и нижнего рассеивающих выпусков производства районных очистных сооружений ооо челныводоканал в Набережных Челнах</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/naberejnye-chelny/92048385-tender-vypolnenie-rabot-po-obsledovaniyu-i-videosemke-verhnego-i-nijnego-rasseivayushchih-vypuskov-proizvodstva-rajonnyh</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>463 600 ₽</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>12.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по созданию видеоконтента в рамках организации и проведения юбилейного fashion-концерта на площадке российского этнографического музея г. санкт-петербург в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/92050963-tender-okazanie-uslugi-po-sozdaniyu-videokontenta-v-ramkah-organizacii-i-provedeniya-yubilejnogo-fashion-koncerta-na-ploshchadke</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>218 000 ₽</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>12.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по по видеосъемке и интернет видео трансляции соревнований в Твери</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>/region/tverskaya-oblast/tver/92047756-tender-okazanie-uslug-po-po-videosemke-i-internet-video-translyacii-sorevnovanij</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>144 000 ₽</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>06.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Тендер на предоставление комплекса услуг по монтажу и техническому обслуживанию оборудования сценического комплекса, его художественному оформлению, а также оснащению средствами видеосъёмки и трансляции для мероприятия в Балашихе</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/balashiha/92046244-tender-predostavlenie-kompleksa-uslug-po-montaju-i-tehnicheskomu-obslujivaniyu-oborudovaniya-scenicheskogo-kompleksa-ego</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению фото- и видеосъемки мероприятия в рамках проведения форума ко дню российского предпринимательства мой бизнес – 2026 в Томске</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>/region/tomskaya-oblast/tomsk/92028045-tender-okazanie-uslug-po-organizacii-i-provedeniyu-foto-i-videosemki-meropriyatiya-v-ramkah-provedeniya-foruma-ko-dnyu-rossijskogo</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>57 833 ₽</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению обучающей программы проводники смыслов. школа молодёжной политики . анализ ситуации в Москве</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/92027962-tender-okazanie-uslug-po-organizacii-i-provedeniyu-obuchayushchej-programmy-provodniki-smyslov-shkola-molodejnoj-politiki-analiz-situacii</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>29 785 302 ₽</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Тендер на проведение видеосъемки и монтажа в рамках организации и проведения xv всероссийского конгресса с международным участием медицина для спорта 2026 в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/92018914-tender-provedenie-videosemki-i-montaja-v-ramkah-organizacii-i-provedeniya-xv</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>131 750 ₽</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и трансляции мероприятий, посвященных празднику 9 мая в Волгограде</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>/region/volgogradskaya-oblast/volgograd/92019211-tender-okazanie-uslug-po-videosemke-i-translyacii-meropriyatij-posvyashchennyh-prazdniku-9-maya</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>249 990 ₽</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по проведению фото и видеосъемки официальных мероприятий, объектов и различных видов производственных процессов</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>/region/voronejskaya-oblast/92017055-tender-vypolnenie-rabot-po-provedeniyu-foto-i-videosemki-oficialnyh-meropriyatij-obektov-i-razlichnyh-vidov-proizvodstvennyh-processov</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>427 000 ₽</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>07.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг профессиональной видеосъемки выставки «металлообработка-2026</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>/tender/30590050974</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>490 000 ₽</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъемки и видеозаписи проведения государственной (итоговой) аттестации в 2026 году</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>/region/primorskij-kraj/91996447-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-gosudarstvennoj-itogovoj-attestacii-v-2026-godu</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>29 746 381 ₽</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>12.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по созданию фото и видеопродукции в Москве</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>/tender/91994241</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>47 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>12.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского семинар-совещания региональных кураторов программы развития социальной активности учащихся начальных классов "орлята россии" в Москве</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/91984931-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-seminar-soveshchaniya-regionalnyh-kuratorov-programmy-razvitiya</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>10 495 000 ₽</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеохудожника в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/91978946-tender-okazanie-uslug-videohudojnika</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеохудожника в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/91978864-tender-okazanie-uslug-videohudojnika</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Тендер на услуги фотосъемки, обработки фотографий</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>/tender/30590050662</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>4 000 ₽</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Тендер организации услуг видеосъемки в Москве</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/91974333-tender-organizacii-uslug-videosemki</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Тендер т7210010.0022. оказание услуг по фото-видеосъемке для нужд пао россети северо-запад в Мурманске</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>/tender/91970561</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>499 999 ₽</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению фотосъемки iii стратегической сессии информационные технологии и языки народов россии в Москве</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/91969181-tender-okazanie-uslug-po-organizacii-i-provedeniyu-fotosemki-iii-strategicheskoj-sessii-informacionnye-tehnologii-i-yazyki-narodov-rossii</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению видеосъёмки и видеозаписи, передачи данных с видеосъемкой основного и дополнительного этапов егэ проведения государственной итоговой аттестации в 2026 году на территории республики тыва в Кызыле</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>/region/tyva-respublika/kyzyl/91965103-tender-okazanie-uslug-po-obespecheniyu-videosemki-i-videozapisi-peredachi-dannyh-s-videosemkoj-osnovnogo-i-dopolnitelnogo-etapov-ege</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>18 733 765 ₽</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению егэ (вчс)</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>/region/tulskaya-oblast/91947118-tender-okazanie-uslug-po-provedeniyu-ege-vchs</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>50 403 ₽</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению егэ (см)</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>/region/tulskaya-oblast/91947121-tender-okazanie-uslug-po-provedeniyu-ege-sm</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>32 022 ₽</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению егэ (см)</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>/region/tulskaya-oblast/91946969-tender-okazanie-uslug-po-provedeniyu-ege-sm</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>32 022 ₽</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rostender_results.xlsx
+++ b/rostender_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D381"/>
+  <dimension ref="A1:D521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8798,6 +8798,3086 @@
         </is>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению ежегодного патриотического фестиваля, посвященного памяти героя российской федерации е.в. фадина в Красногорске</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/krasnogorsk/94631462-tender-okazanie-uslug-po-organizacii-i-provedeniyu-ejegodnogo-patrioticheskogo-festivalya-posvyashchennogo-pamyati-geroya</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>11 903 900 ₽</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации выступления музыкальной группы "abasova", фото- и видеосъёмки, предоставлению сувенирной и подарочной продукции на фестивале "культурный код" в рамках года петербургской культуры в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94622772-tender-okazanie-uslug-po-organizacii-vystupleniya-muzykalnoj-gruppy-abasova-foto-i-videosemki-predostavleniyu-suvenirnoj-i-podarochnoj</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>186 200 ₽</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Тендер на приобретение материальных запасов для кабинета биологии и физики в Югорске</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/yugorsk/94612015-tender-priobretenie-materialnyh-zapasov-dlya-kabineta-biologii-i-fiziki</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Тендер комплект оборудования для видеосъемки и записи звука в Бежецке</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>/region/tverskaya-oblast/bejeck/94607424-tender-komplekt-oborudovaniya-dlya-videosemki-i-zapisi-zvuka</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>79 336 ₽</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение мероприятий. реклама. ритуальные услуги.. услуги видеосъемки, фотосъемки в рамках проведения республиканского фестиваля славянской культуры "славяне xxi века" в рамках дней славянской письменности и культуры в Уфе</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94604996-tender-organizaciya-i-provedenie-meropriyatij-reklama-ritualnye-uslugi-uslugi-videosemki-fotosemki-v-ramkah-provedeniya</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>42 000 ₽</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг в области фото- и видеосъемки событий в Луганске</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>/region/luganskaya-narodnaya-respublika/lugansk/94597556-tender-okazanie-uslug-v-oblasti-foto-i-videosemki-sobytij</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг музыкального редактора по осуществлению художественной видеосъемки концертов в Москве</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>/tender/94598517</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>597 550 ₽</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеооператора и ассистента оператора-постановщика по осуществлению художественной видеосъемки концертов в Москве</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>/tender/94596160</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>598 400 ₽</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеооператора и ассистента оператора-постановщика по осуществлению художественной видеосъемки концертов в Москве</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>/tender/94593571</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>591 800 ₽</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеооператора и ассистента оператора-постановщика по осуществлению художественной видеосъемки концертов в Москве</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>/tender/94592817</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>591 800 ₽</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеооператора и ассистента оператора-постановщика по осуществлению художественной видеосъемки концертов в Москве</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>/tender/94592591</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>591 800 ₽</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеооператора и ассистента оператора-постановщика по осуществлению художественной видеосъемки концертов в Москве</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>/tender/94592364</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>591 800 ₽</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеооператора и ассистента оператора-постановщика по осуществлению художественной видеосъемки концертов в Москве</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>/tender/94592288</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>591 800 ₽</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Тендер зк-№-14936/26 оказание услуг по организации и проведению торжественного собрания в рамках всемирного дня туризма, с целью продвижения туристского потенциала красноярского края в Красноярске</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/94583117-tender-zk-1493626-okazanie-uslug-po-organizacii-i-provedeniyu-torjestvennogo-sobraniya-v-ramkah-vsemirnogo-dnya-turizma-s-celyu</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>3 696 094 ₽</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>03.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Тендер зк-№-14822/26 оказание услуг по организации и проведению форума для представителей туристской индустрии красноярского края в рамках всемирного дня туризма в Красноярске</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/94573264-tender-zk-1482226-okazanie-uslug-po-organizacii-i-provedeniyu-foruma-dlya-predstavitelej-turistskoj-industrii-krasnoyarskogo-kraya</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2 500 000 ₽</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Тендер на закупку на оказание услуг по вывозу и уничтожению некачественной пищевой продукции москва и московская область в Солнечногорске</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>/tender/94570865</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по видеосъемке в Ставрополе</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>/region/stavropolskij-kraj/stavropol/94570460-tender-uslugi-po-videosemke</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>136 666 ₽</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по фотосъемке в Ставрополе</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>/region/stavropolskij-kraj/stavropol/94570422-tender-uslugi-po-fotosemke</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>113 333 ₽</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению организации реализации лучших практик российского образования в области обучения и воспитания на базе образовательных организаций республики абхазия, республики южная осетия, республики армения в Армавире</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/armavir/94555577-tender-okazanie-uslug-po-obespecheniyu-organizacii-realizacii-luchshih-praktik-rossijskogo-obrazovaniya-v-oblasti-obucheniya-i</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>1 051 401 ₽</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке спектакля концертной программы чужие деньги в Волгограде</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>/region/volgogradskaya-oblast/volgograd/94551735-tender-okazanie-uslug-po-videosemke-spektaklya-koncertnoj-programmy-chujie-dengi</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>120 000 ₽</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеосъёмки и монтаж видеоролика в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94542805-tender-okazanie-uslug-videosemki-i-montaj-videorolika</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>60 000 ₽</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организационно-техническому и программно-методическому обеспечению проведения стратегической проектировочной сессии с управленческими командами педагогических вузов (в рамках федерального проекта "педагоги и наставники" национального проекта "молодежь и дети") в Москве</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94531639-tender-okazanie-uslug-po-organizacionno-tehnicheskomu-i-programmno-metodicheskomu-obespecheniyu-provedeniya-strategicheskoj-proektirovochnoj-sessii</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>19 820 962 ₽</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъёмке концертов и торжественных мероприятий в рамках музыкального фестиваля, посвящённого 100?летию санкт?петербургского музыкального училища имени м.п.мусоргского и созданию итогового видеоролика и фильма в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94531888-tender-okazanie-uslug-po-videosemke-koncertov-i-torjestvennyh-meropriyatij-v-ramkah-muzykalnogo-festivalya-posvyashchennogo-100letiyu</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>198 000 ₽</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и изготовлению видеороликов в рамках проведения ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов в Уфе</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94505766-tender-okazanie-uslug-po-videosemke-i-izgotovleniyu-videorolikov-v-ramkah-provedeniya-ii-vserossijskoj-spartakiady-mejdu-subektami</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>360 000 ₽</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению церемонии награждения премии общественной палаты новосибирской области за вклад в развитие благотворительности и добровольчества новосибирской области "во благо" в Новосибирске</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>/region/novosibirskaya-oblast/novosibirsk/94501659-tender-okazanie-uslug-po-organizacii-i-provedeniyu-ceremonii-nagrajdeniya-premii-obshchestvennoj-palaty-novosibirskoj-oblasti</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>240 720 ₽</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации фотосъемки и видеосъемки всероссийского профессионального конкурса лучший учитель родного языка и родной литературы в 2026 году в Липецке</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>/region/lipeckaya-oblast/lipeck/94502505-tender-okazanie-uslug-po-organizacii-fotosemki-i-videosemki-vserossijskogo-professionalnogo-konkursa-luchshij-uchitel-rodnogo-yazyka-i</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>598 000 ₽</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение интерактивной выставки дружба народов</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94473236-tender-organizaciya-i-provedenie-interaktivnoj-vystavki-drujba-narodov</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>311 167 ₽</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Тендер на услуги видеографа и видеомонтажера</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>/region/karachaevo-cherkesskaya-respublika/94452123-tender-uslugi-videografa-i-videomontajera</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>350 000 ₽</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото и видеосъемке и изготовлению видеороликов торжественного мероприятия день знаний в Краснодаре</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/krasnodar/94449122-tender-okazanie-uslug-po-foto-i-videosemke-i-izgotovleniyu-videorolikov-torjestvennogo-meropriyatiya-den-znanij</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>173 000 ₽</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Тендер на приобретение оборудования для фото- и видеосъемки</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/94430835-tender-priobretenie-oborudovaniya-dlya-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>327 360 ₽</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Тендер безопасность и оборудование для ее обеспечения.. фотоаппарат в Салавате</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/salavat/94432149-tender-bezopasnost-i-oborudovanie-dlya-ee-obespecheniya-fotoapparat</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>213 000 ₽</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению игры квн на кубок губернатора ленинградской области цикла региональных мероприятий в рамках поддержки квн ленинградской области</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/94424901-tender-okazanie-uslug-po-organizacii-i-provedeniyu-igry-kvn-na-kubok-gubernatora-leningradskoj-oblasti-cikla-regionalnyh-meropriyatij-v</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2 750 000 ₽</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Тендер на приобретение товаров для нужд воспитательной работы с осужденными в Шагонаре</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>/region/tyva-respublika/shagonar/94397498-tender-priobretenie-tovarov-dlya-nujd-vospitatelnoj-raboty-s-osujdennymi</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>77 999 ₽</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Тендер "оказание услуг по организации и проведению регионального мероприятия в рамках встречи участников проекта "путешествие мечты", проходящего в рамках всероссийского конкурса "большая перемена" в 2026 году в Красноярске</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/94411850-tender-okazanie-uslug-po-organizacii-i-provedeniyu-regionalnogo-meropriyatiya-v-ramkah-vstrechi-uchastnikov-proekta-puteshestvie</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2 397 386 ₽</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского семинар-совещания ведущих экспертов отдела реализации проектов и программ в сфере патриотического воспитания граждан управления реализации федеральных проектов и программ (муниципальных координаторов проекта "навигаторы детства") в Москве</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94363843-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-seminar-soveshchaniya-vedushchih-ekspertov-otdela-realizacii</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>112 071 520 ₽</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по фото - видеосъемке, изготовлению видеороликов для нужд предприятия тимашевские электрические сети филиала пао россети юг - кубаньэнерго в Тимашевске</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/timashevsk/94357258-tender-okazanie-uslug-po-foto-videosemke-izgotovleniyu-videorolikov-dlya-nujd-predpriyatiya-timashevskie-elektricheskie-seti</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>73 200 ₽</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеографа (съемка и монтаж) 8 видеороликов в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/94346260-tender-okazanie-uslug-videografa-semka-i-montaj-8-videorolikov</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>207 008 ₽</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по профессиональной видеосъёмке и фотосъемке мероприятия для участников и ветеранов сво, а также членов их семей в Казани</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/kazan/94336415-tender-okazanie-uslug-po-professionalnoj-videosemke-i-fotosemke-meropriyatiya-dlya-uchastnikov-i-veteranov-svo-a-takje-chlenov-ih</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по обеспечению видеосъемки и видеозаписи проведения дополнительного периода единого государственного экзамена в 2026 году в Орле</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>/region/orlovskaya-oblast/orel/94323818-tender-okazanie-uslugi-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-dopolnitelnogo-perioda-edinogo-gosudarstvennogo-ekzamena-v</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>354 999 ₽</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организацию и проведению фотосьемки в рамках организации и проведения форума работающей молодежи в Барнауле</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/barnaul/94324983-tender-okazanie-uslug-po-organizaciyu-i-provedeniyu-fotosemki-v-ramkah-organizacii-i-provedeniya-foruma-rabotayushchej-molodeji</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>40 000 ₽</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение адаптационного мероприятия "старт в профессию" для лиц, не прошедших государственную итоговую аттестацию по образовательным программам основного общего образования или получивших неудовлетворительные результаты в 2026 году и принятых на программы профессионального обучения в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94313756-tender-organizaciya-i-provedenie-adaptacionnogo-meropriyatiya-start-v-professiyu-dlya-lic-ne-proshedshih-gosudarstvennuyu-itogovuyu</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>3 441 268 ₽</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение карьерного мероприятия для студентов 1 курса спо введение в профессию в профессиональных образовательных организациях санкт-петербурга в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94313771-tender-organizaciya-i-provedenie-karernogo-meropriyatiya-dlya-studentov-1-kursa-spo-vvedenie-v-professiyu-v-professionalnyh-obrazovatelnyh</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>3 564 395 ₽</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>/tender/94311296</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>7 557 600 ₽</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>/tender/94310999</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по созданию видеоконтента об участии делегации тюменской области в форуме молодёжи уральского федерального округа утро в Тюмени</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>/region/tyumenskaya-oblast/tyumen/94304204-tender-uslugi-po-sozdaniyu-videokontenta-ob-uchastii-delegacii-tyumenskoj-oblasti-v-forume-molodeji-uralskogo-federalnogo-okruga-utro</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>167 500 ₽</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Тендер штатив для видеосъемки benro t691+mh2n в Бавлах</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/bavly/94300879-tender-shtativ-dlya-videosemki-benro-t691mh2n</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>4 500 ₽</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение балтийского форума соотечественников в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>/tender/94299020</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>3 420 000 ₽</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>/tender/94291760</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>/tender/94291454</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Тендер демонтаж кингстонной решетки плавдока с видеосъемкой в Астрахани</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>/region/astrahanskaya-oblast/astrahan/94284615-tender-demontaj-kingstonnoj-reshetki-plavdoka-s-videosemkoj</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>262 500 ₽</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>/tender/94280747</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>/tender/94280712</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>7 553 588 ₽</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и изготовлению видеороликов в рамках проведения ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов в Уфе</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94279572-tender-okazanie-uslug-po-videosemke-i-izgotovleniyu-videorolikov-v-ramkah-provedeniya-ii-vserossijskoj-spartakiady-mejdu-subektami</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>360 000 ₽</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации уличного мероприятия огни залива в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94278809-tender-okazanie-uslug-po-organizacii-ulichnogo-meropriyatiya-ogni-zaliva</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>5 669 933 ₽</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Тендер на организацию мероприятий по развитию материально-технической базы государственной образовательной организации в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>/region/sverdlovskaya-oblast/ekaterinburg/94270807-tender-organizaciya-meropriyatij-po-razvitiyu-materialno-tehnicheskoj-bazy-gosudarstvennoj-obrazovatelnoj-organizacii</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>807 920 ₽</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по предоставлению платформы для видеосъемки в формате 360 и фотостойки в рамках мероприятия «обеспечение реализации торжественных мероприятий, посвященных 80-летию образования калининградской области, в муниципальных образованиях калининградской области» (день города ладушкина) в Калининграде</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>/region/kaliningradskaya-oblast/kaliningrad/94268388-tender-uslugi-po-predostavleniyu-platformy-dlya-videosemki-v-formate-360-i-fotostojki-v-ramkah-meropriyatiya-obespechenie</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по обеспечению видеосъемки и видеозаписи проведения дополнительного периода единого государственного экзамена в 2026 году в Орле</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>/region/orlovskaya-oblast/orel/94262092-tender-okazanie-uslugi-po-obespecheniyu-videosemki-i-videozapisi-provedeniya-dopolnitelnogo-perioda-edinogo-gosudarstvennogo-ekzamena-v</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Тендер на услуги в области фото и видеосъемки</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/94260850-tender-uslugi-v-oblasti-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>22 000 ₽</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации репортажной фото- и видеосъемки с изготовлением отчетного видеоролика о проведении 48-й сессии межгосударственного совета по геодезии, картографии, кадастру и дистанционному зондированию земли государств – участников снг в 2026 году в Москве</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94251513-tender-okazanie-uslug-po-organizacii-reportajnoj-foto-i-videosemki-s-izgotovleniem-otchetnogo-videorolika-o-provedenii-48-j-sessii</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Тендер на закупку услуг по профессиональной видеосъемке и аудиозапись онлайн-курсов и высококачественный монтаж видеолекций онлайн-курсов в Москве</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94248963-tender-zakupka-uslug-po-professionalnoj-videosemke-i-audiozapis-onlajn-kursov-i-vysokokachestvennyj-montaj-videolekcij-onlajn-kursov</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>599 518 ₽</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению фото-/видеосъемки здания с использованием специального оборудования (в том числе для высотных работ) в Москве</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94242968-tender-okazanie-uslug-po-provedeniyu-foto-videosemki-zdaniya-s-ispolzovaniem-specialnogo-oborudovaniya-v-tom-chisle-dlya-vysotnyh-rabot</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению фото-/видеосъемки здания с использованием специального оборудования (в том числе для высотных работ) в Москве</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94243808-tender-okazanie-uslug-po-provedeniyu-foto-videosemki-zdaniya-s-ispolzovaniem-specialnogo-oborudovaniya-v-tom-chisle-dlya-vysotnyh-rabot</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение окружных форумов новая философия воспитания в Светлогорске</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>/tender/94223989</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>104 535 650 ₽</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг фотосъемки в рамках проведения ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов в Уфе</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94218751-tender-okazanie-uslug-fotosemki-v-ramkah-provedeniya-ii-vserossijskoj-spartakiady-mejdu-subektami-rossijskoj-federacii-po-letnim</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>264 000 ₽</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и фотосъемке, изготовление отчетного видеофильма по итогам реализации проекта российская национальная премия в сфере креативных индустрий в Москве</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94216604-tender-okazanie-uslug-po-videosemke-i-fotosemke-izgotovlenie-otchetnogo-videofilma-po-itogam-realizacii-proekta-rossijskaya-nacionalnaya-premiya-v</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Тендер на услуги btl мероприятий</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>/region/krym-respublika/94214403-tender-uslugi-btl-meropriyatij</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению фотосъемки по заданию заказчика на территории городского округа реутов в Реутове</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/reutov/94209050-tender-okazanie-uslug-po-provedeniyu-fotosemki-po-zadaniyu-zakazchika-na-territorii-gorodskogo-okruga-reutov</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по видеосъемке и монтажу научно-популярных подкастов (пр) в Якутске</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>/region/saha-yakutiya-respublika/yakutsk/94200293-tender-uslugi-po-videosemke-i-montaju-nauchno-populyarnyh-podkastov-pr</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>82 500 ₽</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Тендер на услуги в области фото и видеосъемки в Альметьевске</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/almetevsk/94195764-tender-uslugi-v-oblasti-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>20 000 ₽</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Тендер на услуги видеооператора в рамках проведения семинара феномен советского общепита. 1920 – 1930-е гг. в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/94180120-tender-uslugi-videooperatora-v-ramkah-provedeniya-seminara-fenomen-sovetskogo-obshchepita-1920-1930-e-gg</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>21 000 ₽</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>09.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Тендер №kffzmu_228_разработка и создание нового видеоматериала "вводный инструктаж" на трех языках в связи с обновлением программы проведения вводного инструктажа, изменениями в структуре подразделении предприятия, а также необходимостью приведения видеоматериала в соответствие с актуальными требованиями охраны труда и промышленной безопасностью</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94155803-tender-kffzmu228razrabotka-i-sozdanie-novogo-videomateriala-vvodnyj-instruktaj-na-treh-yazykah-v-svyazi-s-obnovleniem-programmy-provedeniya-vvodnogo</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъемке и фотосъемке, изготовление отчетного видеофильма по итогам реализации проекта российская национальная премия в сфере креативных индустрий в Москве</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94161141-tender-okazanie-uslug-po-videosemke-i-fotosemke-izgotovlenie-otchetnogo-videofilma-po-itogam-realizacii-proekta-rossijskaya-nacionalnaya-premiya-v</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации видеосъёмки с онлайн-трансляцией мероприятия, оказываемые в рамках комплекса услуг по реализации мероприятия и передать заказчику исключительные права на созданные в процессе оказания услуг результаты интеллектуальной деятельности</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94143153-tender-uslugi-po-organizacii-videosemki-s-onlajn-translyaciej-meropriyatiya-okazyvaemye-v-ramkah-kompleksa-uslug-po-realizacii-meropriyatiya-i</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по осуществлению звукозаписи, видеосъемки и предоставлению во временное пользование экрана в рамках проведения дня гатчинского муниципального округа</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/94131744-tender-okazanie-uslug-po-osushchestvleniyu-zvukozapisi-videosemki-i-predostavleniyu-vo-vremennoe-polzovanie-ekrana-v-ramkah-provedeniya</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>529 900 ₽</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Тендер фото на паспорт в Микуне</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>/region/komi-respublika/mikun/94107080-tender-foto-na-pasport</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>600 ₽</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Тендер на проведение патриотического форум-фестиваля россия начинается здесь (регистрационный номер: 903-а-гз) в Пскове</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>/region/pskovskaya-oblast/pskov/94082791-tender-provedenie-patrioticheskogo-forum-festivalya-rossiya-nachinaetsya-zdes-registracionnyj-nomer-903-a-gz</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>3 017 282 ₽</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по видеосъёмке и видеомонтажу творческих встреч согласно техническому заданию, с отчуждением исключительных прав в Вологде</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>/region/vologodskaya-oblast/vologda/94077325-tender-okazanie-uslug-po-videosemke-i-videomontaju-tvorcheskih-vstrech-soglasno-tehnicheskomu-zadaniyu-s-otchujdeniem-isklyuchitelnyh</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>52 666 ₽</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Тендер на закупку для ао русал менеджмент: услуги фото- и видеосъемки, производства видеороликов для центров спортивных единоборств сокол в 2026-2027 гг в Красноярске</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>/region/krasnoyarskij-kraj/krasnoyarsk/94065743-tender-zakupka-dlya-ao-rusal-menedjment-uslugi-foto-i-videosemki-proizvodstva-videorolikov-dlya-centrov-sportivnyh-edinoborstv</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению финального этапа всероссийского патриотического форума "ступени поколений" в формате молодежного межмуниципального форума "область развития" в рамках реализации программы комплексного развития молодежной политики в ивановской области "регион для молодых" в Иваново</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>/region/ivanovskaya-oblast/ivanovo/94074839-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-finalnogo-etapa-vserossijskogo-patrioticheskogo-foruma-stupeni-pokolenij</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>680 000 ₽</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по созданию видеоконтента (цикла видео-подкастов) в Москве</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94057533-tender-okazanie-uslug-po-sozdaniyu-videokontenta-cikla-video-podkastov</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по фотосъемке городского праздника калуга – наш общий дом 21.08.2026 в городском парке культуры и отдыха в Калуге</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>/region/kalujskaya-oblast/kaluga/94039996-tender-okazanie-uslugi-po-fotosemke-gorodskogo-prazdnika-kaluga-nash-obshchij-dom-21082026-v-gorodskom-parke-kultury-i-otdyha</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение мероприятий. реклама. ритуальные услуги.. оказание услуг по видеосъемке и изготовлению видеороликов в рамках проведения спортивных соревнований по гребному слалому в рамках ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов без ограничений верхней границы возраста 2026 года "спартакиада народов россии" в Уфе</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/94020329-tender-organizaciya-i-provedenie-meropriyatij-reklama-ritualnye-uslugi-okazanie-uslug-po-videosemke-i-izgotovleniyu-videorolikov-v</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>340 000 ₽</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по созданию видеоконтента (цикла видео-подкастов) в Москве</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/94006543-tender-okazanie-uslug-po-sozdaniyu-videokontenta-cikla-video-podkastov</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению фото- и видеосъемки мероприятий проекта "нетрудные" в целях создания лаборатории промышленного дизайна в рамках реализации федерального проекта "регион для молодых" в Всеволожске</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/vsevolojsk/93999334-tender-okazanie-uslug-po-organizacii-i-provedeniyu-foto-i-videosemki-meropriyatij-proekta-netrudnye-v-celyah-sozdaniya</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>598 000 ₽</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по изготовлению сувенирной и полиграфической продукции, а также услуг по фото- и видеосъемке для участников проекта мобильные университетские смены скфо с наукой в села! в Махачкале</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>/region/dagestan-respublika/mahachkala/93998704-tender-okazanie-uslug-po-izgotovleniyu-suvenirnoj-i-poligraficheskoj-produkcii-a-takje-uslug-po-foto-i-videosemke-dlya-uchastnikov</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>1 100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению фотосьемки инклюзивного добровольческого фестиваля добрые люди в Барнауле</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/barnaul/93993934-tender-okazanie-uslug-po-organizacii-i-provedeniyu-fotosemki-inklyuzivnogo-dobrovolcheskogo-festivalya-dobrye-lyudi</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>20 000 ₽</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение мероприятий. реклама. ритуальные услуги.. услуги по видеосъемке и изготовлению видео ролика в рамках проведения спортивных соревнований по велосипедному спорту в рамках ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов без ограничения верхней границы возраста 2026 года в Уфе</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/93978264-tender-organizaciya-i-provedenie-meropriyatij-reklama-ritualnye-uslugi-uslugi-po-videosemke-i-izgotovleniyu-video-rolika-v-ramkah</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>200 000 ₽</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>26.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Тендер на организацию фото- и видеосъёмки в рамках мероприятий для участников проекта медиакласс в московской школе в Москве</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93977257-tender-organizaciya-foto-i-videosemki-v-ramkah-meropriyatij-dlya-uchastnikov-proekta-mediaklass-v-moskovskoj-shkole</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>718 340 ₽</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации и проведению фото- и видеосъемки мероприятия в целях проведения обучающей программы "мама-предприниматель" в Томске</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>/region/tomskaya-oblast/tomsk/93974481-tender-uslugi-po-organizacii-i-provedeniyu-foto-i-videosemki-meropriyatiya-v-celyah-provedeniya-obuchayushchej-programmy-mama</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>53 450 ₽</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг фотографа в рамках проведения второго этапа турнира совета работающей молодёжи алтайского края битва советов в Барнауле</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/barnaul/93967978-tender-okazanie-uslug-fotografa-v-ramkah-provedeniya-vtorogo-etapa-turnira-soveta-rabotayushchej-molodeji-altajskogo-kraya-bitva-sovetov</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>10 000 ₽</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Тендер видеосъемка производства и мероприятия с подготовкой фото- и видеоматериалов в Рязани</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>/region/ryazanskaya-oblast/ryazan/93962872-tender-videosemka-proizvodstva-i-meropriyatiya-s-podgotovkoj-foto-i-videomaterialov</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации экспозиции санкт-петербурга в рамках международной выставки-ярмарки агрорусь в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93936502-tender-okazanie-uslug-po-organizacii-ekspozicii-sankt-peterburga-v-ramkah-mejdunarodnoj-vystavki-yarmarki-agrorus</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>9 825 500 ₽</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по фото, видеосъемке, изготовлению видеографики, организации видеотрансляций и монтажу видеосюжетов о деятельности пао "россети московский регион" для нужд пао "россети московский регион"</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93920166-tender-okazanie-kompleksa-uslug-po-foto-videosemke-izgotovleniyu-videografiki-organizacii-videotranslyacij-i-montaju-videosyujetov-o-deyatelnosti</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>42 128 172 ₽</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по созданию и монтажу видеоролика в Перми</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/perm/93926204-tender-vypolnenie-rabot-po-sozdaniyu-i-montaju-videorolika</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>84 333 ₽</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Тендер на выполнение работ по созданию и монтажу видеоролика в Перми</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>/region/permskij-kraj/perm/93926203-tender-vypolnenie-rabot-po-sozdaniyu-i-montaju-videorolika</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>84 333 ₽</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по информационному сопровождению (фотосъемка, репортажи, публикации в "дневнике смены" и социальных сетях) работы съемочных групп в рамках киносмены; участие в проведении кастинга и кинопроб (фото- и видеосъемка кандидатов); работа в качестве помощника оператора и монтажера, участие в проведении тематических мероприятий киносмены: "корпорация rosson 2.0"</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>/region/leningradskaya-oblast/93918118-tender-uslugi-po-informacionnomu-soprovojdeniyu-fotosemka-reportaji-publikacii-v-dnevnike-smeny-i-socialnyh-setyah-raboty-semochnyh-grupp-v</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>14 942 ₽</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению семинара для представителей военно-патриотических клубов в рамках всероссийского проекта диалоги с героями</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>/region/altajskij-kraj/93916554-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-seminara-dlya-predstavitelej-voenno-patrioticheskih-klubov-v-ramkah-vserossijskogo</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>15 830 000 ₽</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по созданию видеоконтента в рамках организации и проведения театрализованной программы рождение земли югорской в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/93911365-tender-okazanie-uslugi-po-sozdaniyu-videokontenta-v-ramkah-organizacii-i-provedeniya</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>85 000 ₽</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>/region/sverdlovskaya-oblast/93894808-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-videosemki-iili-pryamoj-onlajn-videotranslyacii-v-ramkah-integracii-rossijskogo</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по обеспечению оборудованием в целях организации второго международного фестиваля традиционного и современного этнического творчества "абашевские узоры", разработка светового дизайна и трехмерной модели площадки фестиваля, услуги видеосъемки и онлайн-трансляции в Пензе</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>/region/penzenskaya-oblast/penza/93894935-tender-uslugi-po-obespecheniyu-oborudovaniem-v-celyah-organizacii-vtorogo-mejdunarodnogo-festivalya-tradicionnogo-i-sovremennogo</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>15 126 400 ₽</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации и проведению видеосъемки и/или прямой онлайн-видеотрансляции в рамках интеграции российского общества "знание" в международный фестиваль молодежи 2026 в Екатеринбурге</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>/region/sverdlovskaya-oblast/ekaterinburg/93894403-tender-okazanie-kompleksa-uslug-po-organizacii-i-provedeniyu-videosemki-iili-pryamoj-onlajn-videotranslyacii-v-ramkah</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по фото-и видеосъёмке и изготовлению видеороликов в Владимире</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>/region/vladimirskaya-oblast/vladimir/93891819-tender-uslugi-po-foto-i-videosemke-i-izgotovleniyu-videorolikov</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>498 980 ₽</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по подготовке и проведению, видеосъёмке и созданию видеороликов, организации и оформлению выставочной композиции мероприятия туристической (событийной) направленности "семейный гастрономический фестиваль "деньпельмень" в 2026 году в Комсомольске-на-Амуре</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>/region/habarovskij-kraj/komsomolsk-na-amure/93868543-tender-okazanie-uslug-po-podgotovke-i-provedeniyu-videosemke-i-sozdaniyu-videorolikov-organizacii-i-oformleniyu-vystavochnoj</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>290 276 ₽</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского семинар-совещания главных экспертов отдела реализации проектов и программ в сфере патриотического воспитания граждан управления реализации федеральных проектов и программ (региональных координаторов проекта "навигаторы детства") и главного эксперта отдела международного сотрудничества (республиканского координатора проекта "навигаторы детства республики южная осетия")</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/93855307-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-seminar-soveshchaniya-glavnyh-ekspertov-otdela-realizacii</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>8 283 770 ₽</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Тендер выбор контрагента по оказанию услуг проведения фото-видеосъемки (предпродакшен, продакшен, постпродакшен) для гостиничного оператора cosmos hotel group в Москве</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93827139-tender-vybor-kontragenta-po-okazaniyu-uslug-provedeniya-foto-videosemki-predprodakshen-prodakshen-postprodakshen-dlya-gostinichnogo-operatora-cosmos</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение молодежно-патриотических мероприятий для подростков "не гаснет памяти огонь", проживающих на территории внутригородского муниципального образования города федерального значения санкт-петербурга поселок шушары в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93807259-tender-organizaciya-i-provedenie-molodejno-patrioticheskih-meropriyatij-dlya-podrostkov-ne-gasnet-pamyati-ogon-projivayushchih-na</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>750 000 ₽</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по организации нанесения мурала симбирская чебурашка в рамках мероприятия, связанного с участием в фестивале уличного искусства приволжского федерального округа формарт в Ульяновске</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>/region/ulyanovskaya-oblast/ulyanovsk/93807017-tender-uslugi-po-organizacii-naneseniya-murala-simbirskaya-cheburashka-v-ramkah-meropriyatiya-svyazannogo-s-uchastiem-v-festivale</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>589 500 ₽</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>18.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по созданию видеоконтента в рамках организации и проведения торжественных мероприятий , посвященных празднованию дня работников нефтяной и газовой промышленности в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/hanty-mansijsk/93805171-tender-okazanie-uslugi-po-sozdaniyu-videokontenta-v-ramkah-organizacii-i-provedeniya</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>336 000 ₽</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по созданию видеоконтента в рамках организации и проведения концерта "классика без границ" в исполнении концертного духового оркестра югры и солиста большого театра россии эльчина азизова в Ханты-Мансийске</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>/tender/93805167</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>162 333 ₽</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение мероприятий. реклама. ритуальные услуги.. оказание услуг по видеосъемке и изготовлению видео ролика при проведении спортивных соревнований по триатлону в рамках ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов без ограничения верхней границы возраста 2026 года (далее мероприятия) в Уфе</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/93791832-tender-organizaciya-i-provedenie-meropriyatij-reklama-ritualnye-uslugi-okazanie-uslug-po-videosemke-i-izgotovleniyu-video-rolika-pri</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>260 000 ₽</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по организации и проведению семейного мероприятия для сотрудников в Химках</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/himki/93781566-tender-okazanie-uslugi-po-organizacii-i-provedeniyu-semejnogo-meropriyatiya-dlya-sotrudnikov</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуги по организации и проведению семейного мероприятия для сотрудников в Химках</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/himki/93779064-tender-okazanie-uslugi-po-organizacii-i-provedeniyu-semejnogo-meropriyatiya-dlya-sotrudnikov</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение мероприятий. реклама. ритуальные услуги.. оказание услуг по видеосъемке и изготовлению видео ролика при проведении спортивных соревнований по триатлону в рамках ii всероссийской спартакиады между субъектами российской федерации по летним видам спорта среди сильнейших спортсменов без ограничения верхней границы возраста 2026 года (далее мероприятия) в Уфе</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>/region/bashkortostan-respublika/ufa/93759923-tender-organizaciya-i-provedenie-meropriyatij-reklama-ritualnye-uslugi-okazanie-uslug-po-videosemke-i-izgotovleniyu-video-rolika-pri</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>260 000 ₽</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>16.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по проведению фотосъемки для филиала ириклинская грэс ао интер рао - электрогенерация</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>/region/orenburgskaya-oblast/93735366-tender-uslugi-po-provedeniyu-fotosemki-dlya-filiala-iriklinskaya-gres-ao-inter-rao-elektrogeneraciya</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>65 000 ₽</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению мероприятия семинар-совещание для сотрудников региональных органов власти в рамках реализации конкурса росмолодёжь.гранты в Смоленске</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>/region/smolenskaya-oblast/smolensk/93727927-tender-okazanie-uslug-po-organizacii-i-provedeniyu-meropriyatiya-seminar-soveshchanie-dlya-sotrudnikov-regionalnyh-organov-vlasti-v</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>5 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение научно-методической конференции воспитание созиданием в Санкт-Петербурге</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93727458-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-nauchno-metodicheskoj-konferencii-vospitanie-sozidaniem</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>9 854 722 ₽</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>21.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению семейного мероприятия для сотрудников в Москве</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93720914-tender-okazanie-uslug-po-organizacii-i-provedeniyu-semejnogo-meropriyatiya-dlya-sotrudnikov</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>16.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Тендер фото на паспорт в Микуне</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>/region/komi-respublika/mikun/93722704-tender-foto-na-pasport</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>600 ₽</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по обеспечению фото- и (или) видеосъемки по заказу избирательной комиссии ростовской области в Ростове-на-Дону</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>/region/rostovskaya-oblast/rostov-na-donu/93658683-tender-okazanie-uslug-po-obespecheniyu-foto-i-ili-videosemki-po-zakazu-izbiratelnoj-komissii-rostovskoj-oblasti</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению церемонии закрытия региональных этапов чемпионата профессионалов в 2026 г. на полигоне приволжской железной дороги в Энгельсе</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>/region/saratovskaya-oblast/engels/93669949-tender-okazanie-uslug-po-provedeniyu-ceremonii-zakrytiya-regionalnyh-etapov-chempionata-professionalov-v-2026-g-na-poligone</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>1 108 583 ₽</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Тендер предметная видеосъёмка (мониторинг) в Красногорске</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>/region/moskovskaya-oblast/krasnogorsk/93659828-tender-predmetnaya-videosemka-monitoring</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по предмету: организация и проведение всероссийского фестиваля детского творчества вдохновленные детством в Москве</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93667673-tender-okazanie-kompleksa-uslug-po-predmetu-organizaciya-i-provedenie-vserossijskogo-festivalya-detskogo-tvorchestva-vdohnovlennye-detstvom</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>9 527 509 ₽</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение досуговых мероприятий для жителей внутригородского муниципального образования города федерального значения санкт-петербурга поселок шушары</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93665784-tender-organizaciya-i-provedenie-dosugovyh-meropriyatij-dlya-jitelej-vnutrigorodskogo-municipalnogo-obrazovaniya-goroda-federalnogo</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>948 989 ₽</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Тендер на изготовление видеоролика с использованием квадрокоптера (с прошивкой для возможности использования над водой) в течение 2-х полных дней (зерновой терминал г. азов) в Азове</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>/region/rostovskaya-oblast/azov/93665496-tender-izgotovlenie-videorolika-s-ispolzovaniem-kvadrokoptera-s-proshivkoj-dlya-vozmojnosti-ispolzovaniya-nad-vodoj-v-techenie-2-h-polnyh</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Тендер цифровая техника, прочее, устройства запоминающие внешние, ip оборудование, фото/видео техника/оптика и оборудование, видеокамеры в Анапе</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/anapa/93660949-tender-cifrovaya-tehnika-prochee-ustrojstva-zapominayushchie-vneshnie-ip-oborudovanie-fotovideo-tehnikaoptika-i-oborudovanie-videokamery</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>164 829 ₽</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по проведению видеосъемки, трансляции в интернет и на средства видеоотображения коллективного мероприятия в городах рф в Москве</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>/tender/93644172</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Тендер услуга по техническому и программному обеспечению видеосъемки проведения специализированного клинического интервью по стандартизированной операционной процедуре проведения этологического исследования с использованием биометрической видеорегистрации</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93637060-tender-usluga-po-tehnicheskomu-i-programmnomu-obespecheniyu-videosemki-provedeniya-specializirovannogo-klinicheskogo-intervyu-po</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по проведению видеосъемки и монтажу видеороликов для нужд администрации муниципального образования апшеронский район в Апшеронске</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/apsheronsk/93635751-tender-uslugi-po-provedeniyu-videosemki-i-montaju-videorolikov-dlya-nujd-administracii-municipalnogo-obrazovaniya-apsheronskij</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>449 800 ₽</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Тендер на организацию и проведение военно-тактической игры для подростков внутригородского муниципального образования города федерального значения санкт-петербурга поселок шушары</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93614334-tender-organizaciya-i-provedenie-voenno-takticheskoj-igry-dlya-podrostkov-vnutrigorodskogo-municipalnogo-obrazovaniya-goroda-federalnogo</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>610 050 ₽</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации и проведению мероприятий "россия - родина моя" и "слава россии" для жителей внутригородского муниципального образования города федерального значения санкт-петербурга поселок шушары</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>/region/sankt-peterburg-gorod/93614108-tender-okazanie-uslug-po-organizacii-i-provedeniyu-meropriyatij-rossiya-rodina-moya-i-slava-rossii-dlya-jitelej-vnutrigorodskogo</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>493 867 ₽</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Тендер на услуги в области фото и видеосъемки в Нижнекамске</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>/region/tatarstan-respublika/nijnekamsk/93606985-tender-uslugi-v-oblasti-foto-i-videosemki</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>200 ₽</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по проведению церемонии закрытия региональных этапов чемпионата профессионалов в 2026 г. на полигоне приволжской железной дороги в Энгельсе</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>/region/saratovskaya-oblast/engels/93603975-tender-okazanie-uslug-po-provedeniyu-ceremonii-zakrytiya-regionalnyh-etapov-chempionata-professionalov-v-2026-g-na-poligone</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>1 108 583 ₽</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг видеосъёмки и монтаж мультимедийного проекта в Кургане</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>/region/kurganskaya-oblast/kurgan/93594523-tender-okazanie-uslug-videosemki-i-montaj-multimedijnogo-proekta</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>30 000 ₽</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Тендер услуг по видеосъемке строящихся и готовых объектов, курируемых министерством строительства кузбасса</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>/region/kemerovskaya-oblast/93587797-tender-uslug-po-videosemke-stroyashchihsya-i-gotovyh-obektov-kuriruemyh-ministerstvom-stroitelstva-kuzbassa</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>162 000 ₽</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по организации видеосъемки и монтажу короткометражного фильма в Сургуте</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/surgut/93559703-tender-okazanie-uslug-po-organizacii-videosemki-i-montaju-korotkometrajnogo-filma</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>100 000 ₽</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Тендер на оказание комплекса услуг по организации всероссийского форума пик возможностей в Москве</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93557243-tender-okazanie-kompleksa-uslug-po-organizacii-vserossijskogo-foruma-pik-vozmojnostej</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по сопровождению открытого корпоративного чемпионата профессионального мастерства группы компаний "россети" по стандартам автономной некоммерческой организации "агентство развития профессионального мастерства (ворлдскиллс россия)", по компетенции "техническое обслуживание и ремонт распределительных сетей 0,4-20кв" с организацией видеосъёмки и созданием видеороликов для нужд филиала пао "россети юг" - "кубаньэнерго" в Краснодаре</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>/region/krasnodarskij-kraj/krasnodar/93555140-tender-okazanie-uslug-po-soprovojdeniyu-otkrytogo-korporativnogo-chempionata-professionalnogo-masterstva-gruppy-kompanij-rosseti-po</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>472 140 ₽</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по монтажу видеороликов по материалам заказчика в Москве</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>/region/moskva-gorod/93551119-tender-okazanie-uslug-po-montaju-videorolikov-po-materialam-zakazchika</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>1 359 803 ₽</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Тендер на оказание услуг по удалению сточных отходов (жбо) для нужд казенного учреждения ханты-мансийского автономного округа – югры центроспас-югория</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>/region/hanty-mansijskij-avtonomnyj-okrug---yugra-avtonomnyj-okrug/93545668-tender-okazanie-uslug-po-udaleniyu-stochnyh-othodov-jbo-dlya-nujd-kazennogo-uchrejdeniya-hanty</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Тендер на услуги по фото- и видеосъемке и изготовлению видеоконтента для нужд филиала пао россети центр и приволжье – удмуртэнерго</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>/region/udmurtskaya-respublika/93522636-tender-uslugi-po-foto-i-videosemke-i-izgotovleniyu-videokontenta-dlya-nujd-filiala-pao-rosseti-centr-i-privolje-udmurtenergo</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>349 999 ₽</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
